--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -878,127 +878,127 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>59.51</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>465573.8</t>
+          <t>437969.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>579417.88</t>
+          <t>570563.3</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-18693.88</v>
+        <v>-22149.96</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,42 +1177,42 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,22 +1334,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.74</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>452042.6</t>
+          <t>465573.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>596784.86</t>
+          <t>579417.88</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-8684.33</v>
+        <v>-18693.88</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,42 +1608,42 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>445047.0</t>
+          <t>452042.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>643736.64</t>
+          <t>596784.86</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>9413.950000000001</v>
+        <v>-8684.33</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15157.0</t>
+          <t>8540.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,47 +2302,47 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>58.24000000000001</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2357,22 +2357,22 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>937479.0</t>
+          <t>517165.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>393702.8</t>
+          <t>445047.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>303455.3</t>
+          <t>339942.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>659423.84</t>
+          <t>643736.64</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-60285.40158650742</t>
+          <t>-49562.42385215155</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>1985.04</v>
+        <v>9413.950000000001</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>15157.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>75.54</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>57.26000000000001</t>
+          <t>58.24000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>421351.0</t>
+          <t>937479.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>275060.4</t>
+          <t>393702.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>234213.9</t>
+          <t>303455.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>643815.04</t>
+          <t>659423.84</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-71607.30094654183</t>
+          <t>-60285.40158650742</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-53732.22</v>
+        <v>1985.04</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,42 +3033,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7091.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-3.27</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3057.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.68</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>57.26000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-203.28</t>
+          <t>-89.66</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.96</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>174562.0</t>
+          <t>421351.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>218033.2</t>
+          <t>275060.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>218350.5</t>
+          <t>234213.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>642009.16</t>
+          <t>643815.04</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-317</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-74857.31579659131</t>
+          <t>-71607.30094654183</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-76109.87</v>
+        <v>-53732.22</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,42 +3332,42 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>57.7</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3065.0</t>
+          <t>3057.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,275 +3595,275 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.04</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.76</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-203.28</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-105.96</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>819526.3304347827</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>174562.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>218033.2</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>218350.5</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>642009.16</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-317</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-74857.31579659131</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>-76109.87</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>24.72</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>43.93</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>34629</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>57.0</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-464.25</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-102.93</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>820098.9492017417</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>174678.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>212521.0</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>227616.4</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>643094.8</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-15095</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-74629.57784452781</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-78918.07000000001</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-3.841141774361624</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>34.73629981257034</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>32.80397526962716</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>44.82</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>35642</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>56.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4712.0</t>
+          <t>3065.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>59.76</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-3104.58</t>
+          <t>-464.25</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-99.53</t>
+          <t>-102.93</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>260444.0</t>
+          <t>174678.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>234838.0</t>
+          <t>212521.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>255984.1</t>
+          <t>227616.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>641889.36</t>
+          <t>643094.8</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-21146</t>
+          <t>-15095</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-73849.85288862225</t>
+          <t>-74629.57784452781</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-80123.69</v>
+        <v>-78918.07000000001</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,42 +4194,42 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5987.0</t>
+          <t>4712.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.62</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>58.77999999999999</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>61.17</t>
+          <t>60.88</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.62</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>56.92</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-308.20</t>
+          <t>-3104.58</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-95.87</t>
+          <t>-99.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>344267.0</t>
+          <t>260444.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>213207.8</t>
+          <t>234838.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>265240.8</t>
+          <t>255984.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>639604.54</t>
+          <t>641889.36</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-52033</t>
+          <t>-21146</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-72709.154839041</t>
+          <t>-73849.85288862225</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-88173.67</v>
+        <v>-80123.69</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,42 +4625,42 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2301.0</t>
+          <t>5987.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-19.62</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>59.48</t>
+          <t>58.77999999999999</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>61.17</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.55</t>
+          <t>59.62</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.92</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-144.98</t>
+          <t>-308.20</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-92.69</t>
+          <t>-95.87</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>136215.0</t>
+          <t>344267.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>193367.4</t>
+          <t>213207.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>272587.5</t>
+          <t>265240.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>637064.6</t>
+          <t>639604.54</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-79220</t>
+          <t>-52033</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-69897.42474011309</t>
+          <t>-72709.154839041</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-105505.62</v>
+        <v>-88173.67</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2470.0</t>
+          <t>2301.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-35.46</t>
+          <t>-29.06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5319,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>59.84</t>
+          <t>59.48</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>61.58</t>
+          <t>61.43</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>59.55</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>56.81</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-106.86</t>
+          <t>-144.98</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-90.04</t>
+          <t>-92.69</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>820098.9492017417</t>
+          <t>819526.3304347827</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>147001.0</t>
+          <t>136215.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>218667.8</t>
+          <t>193367.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>338806.2</t>
+          <t>272587.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>640131.16</t>
+          <t>637064.6</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-120138</t>
+          <t>-79220</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-63423.20826936791</t>
+          <t>-69897.42474011309</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-104206.19</v>
+        <v>-105505.62</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-3.841141774361624</t>
+          <t>-1.228328584465341</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>34.73629981257034</t>
+          <t>47.44460114587924</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>32.80397526962716</t>
+          <t>32.54445648609581</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,72 +893,72 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>59.51</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.11</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>437969.2</t>
+          <t>289419.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>570563.3</t>
+          <t>568481.84</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-22149.96</v>
+        <v>-30660.24</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,127 +1309,127 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>59.51</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>465573.8</t>
+          <t>437969.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>579417.88</t>
+          <t>570563.3</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-18693.88</v>
+        <v>-22149.96</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,22 +1765,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.74</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>452042.6</t>
+          <t>465573.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>596784.86</t>
+          <t>579417.88</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-8684.33</v>
+        <v>-18693.88</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>445047.0</t>
+          <t>452042.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>643736.64</t>
+          <t>596784.86</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>9413.950000000001</v>
+        <v>-8684.33</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15157.0</t>
+          <t>8540.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,47 +2733,47 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>58.24000000000001</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2788,22 +2788,22 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>937479.0</t>
+          <t>517165.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>393702.8</t>
+          <t>445047.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>303455.3</t>
+          <t>339942.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>659423.84</t>
+          <t>643736.64</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-60285.40158650742</t>
+          <t>-49562.42385215155</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>1985.04</v>
+        <v>9413.950000000001</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>15157.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>75.54</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>57.26000000000001</t>
+          <t>58.24000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>421351.0</t>
+          <t>937479.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>275060.4</t>
+          <t>393702.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>234213.9</t>
+          <t>303455.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>643815.04</t>
+          <t>659423.84</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-71607.30094654183</t>
+          <t>-60285.40158650742</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-53732.22</v>
+        <v>1985.04</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3057.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>57.26000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-203.28</t>
+          <t>-89.66</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.96</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>174562.0</t>
+          <t>421351.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>218033.2</t>
+          <t>275060.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>218350.5</t>
+          <t>234213.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>642009.16</t>
+          <t>643815.04</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-317</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-74857.31579659131</t>
+          <t>-71607.30094654183</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-76109.87</v>
+        <v>-53732.22</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>57.7</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3065.0</t>
+          <t>3057.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,275 +4026,275 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.04</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.76</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-203.28</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-105.96</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>818763.0455861071</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>174562.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>218033.2</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>218350.5</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>642009.16</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-317</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-74857.31579659131</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-76109.87</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>24.43</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>42.34</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>34212</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>57.0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-464.25</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-102.93</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>819526.3304347827</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>174678.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>212521.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>227616.4</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>643094.8</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-15095</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-74629.57784452781</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-78918.07000000001</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>24.72</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>43.93</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>34629</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>56.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4712.0</t>
+          <t>3065.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>59.76</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-3104.58</t>
+          <t>-464.25</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-99.53</t>
+          <t>-102.93</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>260444.0</t>
+          <t>174678.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>234838.0</t>
+          <t>212521.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>255984.1</t>
+          <t>227616.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>641889.36</t>
+          <t>643094.8</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-21146</t>
+          <t>-15095</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-73849.85288862225</t>
+          <t>-74629.57784452781</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-80123.69</v>
+        <v>-78918.07000000001</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5987.0</t>
+          <t>4712.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-19.62</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>58.77999999999999</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>61.17</t>
+          <t>60.88</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.62</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>56.92</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-308.20</t>
+          <t>-3104.58</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-95.87</t>
+          <t>-99.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>344267.0</t>
+          <t>260444.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>213207.8</t>
+          <t>234838.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>265240.8</t>
+          <t>255984.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>639604.54</t>
+          <t>641889.36</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-52033</t>
+          <t>-21146</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-72709.154839041</t>
+          <t>-73849.85288862225</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-88173.67</v>
+        <v>-80123.69</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2301.0</t>
+          <t>5987.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-19.62</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>59.48</t>
+          <t>58.77999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>61.17</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.55</t>
+          <t>59.62</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.92</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-144.98</t>
+          <t>-308.20</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-92.69</t>
+          <t>-95.87</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>819526.3304347827</t>
+          <t>818763.0455861071</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>136215.0</t>
+          <t>344267.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>193367.4</t>
+          <t>213207.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>272587.5</t>
+          <t>265240.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>637064.6</t>
+          <t>639604.54</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-79220</t>
+          <t>-52033</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-69897.42474011309</t>
+          <t>-72709.154839041</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-105505.62</v>
+        <v>-88173.67</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,142 +1009,142 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>59.01</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>60.14</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>817966.6647398844</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>221675.6</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>566147.36</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-37072.39</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>818763.0455861071</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-30660.24</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BF2" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,72 +1324,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>59.51</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.11</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>437969.2</t>
+          <t>289419.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>570563.3</t>
+          <t>568481.84</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-22149.96</v>
+        <v>-30660.24</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,127 +1740,127 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-2.79</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>59.51</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>465573.8</t>
+          <t>437969.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>579417.88</t>
+          <t>570563.3</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-18693.88</v>
+        <v>-22149.96</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,22 +2196,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.74</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>452042.6</t>
+          <t>465573.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>596784.86</t>
+          <t>579417.88</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-8684.33</v>
+        <v>-18693.88</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>445047.0</t>
+          <t>452042.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>643736.64</t>
+          <t>596784.86</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>9413.950000000001</v>
+        <v>-8684.33</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15157.0</t>
+          <t>8540.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,47 +3164,47 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>58.24000000000001</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>937479.0</t>
+          <t>517165.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>393702.8</t>
+          <t>445047.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>303455.3</t>
+          <t>339942.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>659423.84</t>
+          <t>643736.64</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-60285.40158650742</t>
+          <t>-49562.42385215155</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>1985.04</v>
+        <v>9413.950000000001</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>15157.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>75.54</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.26000000000001</t>
+          <t>58.24000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>421351.0</t>
+          <t>937479.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>275060.4</t>
+          <t>393702.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>234213.9</t>
+          <t>303455.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>643815.04</t>
+          <t>659423.84</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-71607.30094654183</t>
+          <t>-60285.40158650742</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-53732.22</v>
+        <v>1985.04</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3057.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>57.26000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-203.28</t>
+          <t>-89.66</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.96</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>174562.0</t>
+          <t>421351.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>218033.2</t>
+          <t>275060.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>218350.5</t>
+          <t>234213.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>642009.16</t>
+          <t>643815.04</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-317</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-74857.31579659131</t>
+          <t>-71607.30094654183</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-76109.87</v>
+        <v>-53732.22</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>57.7</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3065.0</t>
+          <t>3057.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,275 +4457,275 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.04</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.76</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-203.28</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-105.96</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>817966.6647398844</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>174562.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>218033.2</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>218350.5</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>642009.16</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-317</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-74857.31579659131</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>-76109.87</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>24.51</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>41.96</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>34331</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>57.0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-464.25</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-102.93</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>818763.0455861071</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>174678.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>212521.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>227616.4</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>643094.8</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-15095</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-74629.57784452781</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-78918.07000000001</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>24.43</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>42.34</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>34212</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>56.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4712.0</t>
+          <t>3065.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>59.76</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-3104.58</t>
+          <t>-464.25</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-99.53</t>
+          <t>-102.93</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>260444.0</t>
+          <t>174678.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>234838.0</t>
+          <t>212521.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>255984.1</t>
+          <t>227616.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>641889.36</t>
+          <t>643094.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-21146</t>
+          <t>-15095</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-73849.85288862225</t>
+          <t>-74629.57784452781</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-80123.69</v>
+        <v>-78918.07000000001</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5987.0</t>
+          <t>4712.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.62</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>58.77999999999999</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>61.17</t>
+          <t>60.88</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.62</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>56.92</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-308.20</t>
+          <t>-3104.58</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-95.87</t>
+          <t>-99.53</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>818763.0455861071</t>
+          <t>817966.6647398844</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>344267.0</t>
+          <t>260444.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>213207.8</t>
+          <t>234838.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>265240.8</t>
+          <t>255984.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>639604.54</t>
+          <t>641889.36</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-52033</t>
+          <t>-21146</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-72709.154839041</t>
+          <t>-73849.85288862225</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-88173.67</v>
+        <v>-80123.69</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>60.14</t>
+          <t>60.16</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>221675.6</t>
+          <t>235377.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>566147.36</t>
+          <t>560862.08</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-37072.39</v>
+        <v>-33155.15</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,142 +1440,142 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>59.01</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>60.14</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>817388.4242424243</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>221675.6</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>566147.36</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>-37072.39</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>817966.6647398844</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-30660.24</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BF3" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,72 +1755,72 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.87</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>59.51</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.11</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>437969.2</t>
+          <t>289419.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>570563.3</t>
+          <t>568481.84</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-22149.96</v>
+        <v>-30660.24</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,127 +2171,127 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-2.43</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>59.51</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>465573.8</t>
+          <t>437969.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>579417.88</t>
+          <t>570563.3</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-18693.88</v>
+        <v>-22149.96</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.74</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>452042.6</t>
+          <t>465573.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>596784.86</t>
+          <t>579417.88</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-8684.33</v>
+        <v>-18693.88</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>445047.0</t>
+          <t>452042.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>643736.64</t>
+          <t>596784.86</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>9413.950000000001</v>
+        <v>-8684.33</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15157.0</t>
+          <t>8540.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,47 +3595,47 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>58.24000000000001</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3650,22 +3650,22 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>937479.0</t>
+          <t>517165.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>393702.8</t>
+          <t>445047.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>303455.3</t>
+          <t>339942.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>659423.84</t>
+          <t>643736.64</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-60285.40158650742</t>
+          <t>-49562.42385215155</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>1985.04</v>
+        <v>9413.950000000001</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>15157.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>75.54</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.26000000000001</t>
+          <t>58.24000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>421351.0</t>
+          <t>937479.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>275060.4</t>
+          <t>393702.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>234213.9</t>
+          <t>303455.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>643815.04</t>
+          <t>659423.84</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-71607.30094654183</t>
+          <t>-60285.40158650742</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-53732.22</v>
+        <v>1985.04</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3057.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>57.26000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-203.28</t>
+          <t>-89.66</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.96</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>174562.0</t>
+          <t>421351.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>218033.2</t>
+          <t>275060.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>218350.5</t>
+          <t>234213.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>642009.16</t>
+          <t>643815.04</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-317</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-74857.31579659131</t>
+          <t>-71607.30094654183</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-76109.87</v>
+        <v>-53732.22</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>57.7</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3065.0</t>
+          <t>3057.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,275 +4888,275 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.04</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.76</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-203.28</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-105.96</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>817388.4242424243</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>174562.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>218033.2</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>218350.5</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>642009.16</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-317</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-74857.31579659131</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-76109.87</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>25.02</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>42.77</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>35046</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>57.0</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-464.25</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-102.93</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>817966.6647398844</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>174678.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>212521.0</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>227616.4</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>643094.8</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-15095</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-74629.57784452781</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-78918.07000000001</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>24.51</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>41.96</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>34331</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>56.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4712.0</t>
+          <t>3065.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>59.76</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-3104.58</t>
+          <t>-464.25</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-99.53</t>
+          <t>-102.93</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>817966.6647398844</t>
+          <t>817388.4242424243</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>260444.0</t>
+          <t>174678.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>234838.0</t>
+          <t>212521.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>255984.1</t>
+          <t>227616.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>641889.36</t>
+          <t>643094.8</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-21146</t>
+          <t>-15095</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-73849.85288862225</t>
+          <t>-74629.57784452781</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-80123.69</v>
+        <v>-78918.07000000001</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,288 +1014,293 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>58.66</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>60.11</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>57.83</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-36.02</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-109.54</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>816801.7154178674</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>273475.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>241628.6</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>353601.2</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>558552.82</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-111972</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-34739.56216577447</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-29935.8845248259</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>273475</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>60.16</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>57.77</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-14.48</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-108.68</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>817388.4242424243</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>278164.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>235377.2</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>343709.9</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>560862.08</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-108332</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-35612.95810049239</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-33155.15</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-4.58</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>58.8</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>60.14</t>
+          <t>60.16</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>817388.4242424243</t>
+          <t>816801.7154178674</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>221675.6</t>
+          <t>235377.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>566147.36</t>
+          <t>560862.08</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-37072.39</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-35612.95810049239</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-33155.15262150689</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>278164</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-2.21</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,288 +1886,293 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>59.01</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>60.14</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>816801.7154178674</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>221675.6</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>566147.36</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>178445</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>817388.4242424243</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-30660.24</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-2.21</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,72 +2206,72 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2266,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>59.51</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.11</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>817388.4242424243</t>
+          <t>816801.7154178674</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>437969.2</t>
+          <t>289419.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>570563.3</t>
+          <t>568481.84</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-22149.96</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
+          <t>-35875.73082668789</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-30660.24445832073</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>194731</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>59.8</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2602,127 +2627,127 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>59.51</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>817388.4242424243</t>
+          <t>816801.7154178674</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>465573.8</t>
+          <t>437969.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>579417.88</t>
+          <t>570563.3</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-18693.88</v>
-      </c>
-      <c r="BD6" t="inlineStr">
+          <t>-36824.00107548192</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-22149.96022690379</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>283328</v>
+      </c>
+      <c r="BE6" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-1.36</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>59.3</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,27 +3088,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3113,7 +3143,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.74</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>817388.4242424243</t>
+          <t>816801.7154178674</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>452042.6</t>
+          <t>465573.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>596784.86</t>
+          <t>579417.88</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-8684.33</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-39492.00850249613</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-18693.87703106157</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>242218</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>817388.4242424243</t>
+          <t>816801.7154178674</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>445047.0</t>
+          <t>452042.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>643736.64</t>
+          <t>596784.86</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>9413.950000000001</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-43273.48695184787</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-8684.334000177623</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>209656</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>61.7</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15157.0</t>
+          <t>8540.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,47 +4066,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>58.24000000000001</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4081,22 +4121,22 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>817388.4242424243</t>
+          <t>816801.7154178674</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>937479.0</t>
+          <t>517165.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>393702.8</t>
+          <t>445047.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>303455.3</t>
+          <t>339942.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>659423.84</t>
+          <t>643736.64</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-60285.40158650742</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>1985.04</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-49562.42385215155</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>9413.953686805733</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>517165</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>4.58</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>2.68</t>
-        </is>
-      </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>15157.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>75.54</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.26000000000001</t>
+          <t>58.24000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,180 +4592,180 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>817388.4242424243</t>
+          <t>816801.7154178674</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>421351.0</t>
+          <t>937479.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>275060.4</t>
+          <t>393702.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>234213.9</t>
+          <t>303455.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>643815.04</t>
+          <t>659423.84</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-71607.30094654183</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-53732.22</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-60285.40158650742</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>1985.044893681828</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>937479</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>4.58</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4730,15 +4775,20 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>61.6</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3057.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>57.26000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-203.28</t>
+          <t>-89.66</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.96</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,172 +5028,172 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>817388.4242424243</t>
+          <t>816801.7154178674</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>174562.0</t>
+          <t>421351.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>218033.2</t>
+          <t>275060.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>218350.5</t>
+          <t>234213.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>642009.16</t>
+          <t>643815.04</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-317</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-74857.31579659131</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-76109.87</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-71607.30094654183</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-53732.21927126963</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>421351</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
           <t>57.7</t>
@@ -5151,25 +5201,30 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3065.0</t>
+          <t>3057.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,288 +5374,293 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.04</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.76</t>
+          <t>59.83</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-203.28</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-105.96</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>816801.7154178674</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>174562.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>218033.2</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>218350.5</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>642009.16</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-317</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-74857.31579659131</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-76109.8745329406</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>174562</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>41.57</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>33496</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>57.0</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-464.25</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-102.93</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>817388.4242424243</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>174678.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>212521.0</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>227616.4</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>643094.8</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-15095</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-74629.57784452781</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-78918.07000000001</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>35046</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>60.11</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>241628.6</t>
+          <t>212208.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>558552.82</t>
+          <t>556448.64</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>273475</v>
+        <v>136228</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,147 +1450,147 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>58.66</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>60.11</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>57.83</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-36.02</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-109.54</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>815920.4784172662</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>273475.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>241628.6</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>353601.2</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>558552.82</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-111972</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-34739.56216577447</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-29935.8845248259</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>273475</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>60.16</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>57.77</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-14.48</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-108.68</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>816801.7154178674</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>278164.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>235377.2</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>343709.9</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>560862.08</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-108332</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-35612.95810049239</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-33155.15262150689</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>278164</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG3" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>60.14</t>
+          <t>60.16</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>221675.6</t>
+          <t>235377.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>566147.36</t>
+          <t>560862.08</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>178445</v>
+        <v>278164</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,147 +2322,147 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>59.01</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>60.14</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>815920.4784172662</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>221675.6</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>566147.36</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>178445</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>816801.7154178674</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>194731</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,72 +2642,72 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-3.38</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>59.51</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,50 +2848,50 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>437969.2</t>
+          <t>289419.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>570563.3</t>
+          <t>568481.84</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-22149.96022690379</t>
+          <t>-30660.24445832073</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>283328</v>
+        <v>194731</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,127 +3063,127 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-2.29</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-4.98</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>59.51</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>465573.8</t>
+          <t>437969.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>579417.88</t>
+          <t>570563.3</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-18693.87703106157</t>
+          <t>-22149.96022690379</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>242218</v>
+        <v>283328</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,22 +3524,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.74</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,50 +3720,50 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>452042.6</t>
+          <t>465573.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>596784.86</t>
+          <t>579417.88</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-8684.334000177623</t>
+          <t>-18693.87703106157</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>209656</v>
+        <v>242218</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>60.08</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>445047.0</t>
+          <t>452042.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>643736.64</t>
+          <t>596784.86</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>9413.953686805733</t>
+          <t>-8684.334000177623</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>517165</v>
+        <v>209656</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15157.0</t>
+          <t>8540.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,47 +4502,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>58.24000000000001</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4557,22 +4557,22 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.82</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>937479.0</t>
+          <t>517165.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>393702.8</t>
+          <t>445047.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>303455.3</t>
+          <t>339942.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>659423.84</t>
+          <t>643736.64</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>105104</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-60285.40158650742</t>
+          <t>-49562.42385215155</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1985.044893681828</t>
+          <t>9413.953686805733</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>937479</v>
+        <v>517165</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>15157.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>75.54</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.26000000000001</t>
+          <t>58.24000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>60.08</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>421351.0</t>
+          <t>937479.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>275060.4</t>
+          <t>393702.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>234213.9</t>
+          <t>303455.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>643815.04</t>
+          <t>659423.84</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-71607.30094654183</t>
+          <t>-60285.40158650742</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-53732.21927126963</t>
+          <t>1985.044893681828</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>421351</v>
+        <v>937479</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3057.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>57.26000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.13</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.83</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-203.28</t>
+          <t>-89.66</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.96</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>816801.7154178674</t>
+          <t>815920.4784172662</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>174562.0</t>
+          <t>421351.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>218033.2</t>
+          <t>275060.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>218350.5</t>
+          <t>234213.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>642009.16</t>
+          <t>643815.04</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-317</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-74857.31579659131</t>
+          <t>-71607.30094654183</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-76109.8745329406</t>
+          <t>-53732.21927126963</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>174562</v>
+        <v>421351</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>57.7</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ2"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2826.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,37 +928,37 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-17 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-03 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -983,324 +983,4684 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>35.71</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-1.69</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-3.21</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>57.16</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>58.14</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>60.07</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>58.08</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-24.14</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.80</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-112.17</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>162030.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>209836.2</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>215755.9</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>550120.9</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-5919</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-35791.36830932057</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-38160.02218378661</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>162030</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-2.89</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>56.9</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3484.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-15.18</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-2.24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>-2.29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>16.67</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>10.56</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>-0.77</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-1.80</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-2.94</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>57.23999999999999</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>58.29</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>60.05</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>57.99</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-32.85</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.81</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-111.43</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>199284.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>213119.2</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>251269.4</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>555483.94</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-38150</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-35360.70396850856</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-36671.78477886959</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>199284</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-3.57</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2408.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-34.72</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-2.24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>16.11</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-2.71</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>58.46</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>60.09</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>57.91</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-36.35</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-110.50</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>136228.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>212208.6</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>325088.9</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>556448.64</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-112880</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-35122.32563935201</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-37227.52474402849</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>136228</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-3.57</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>56.1</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4791.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-31.67</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-3.27</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>8.27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>15.46</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-1.76</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>57.62</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>58.66</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>60.11</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>57.83</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-36.02</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-109.54</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>273475.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>241628.6</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>353601.2</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>558552.82</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-111972</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-34739.56216577447</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-29935.8845248259</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>273475</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-4.58</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>58.7</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4747.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-2.8</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-31.52</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>8.19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>19.01</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-2.1</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>58.17999999999999</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>60.16</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>57.77</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-14.48</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.53</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-108.68</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>278164.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>235377.2</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>343709.9</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>560862.08</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-108332</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-35612.95810049239</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-33155.15262150689</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>278164</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3082.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-33.50</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>13.04</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-1.34</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>59.01</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>60.14</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>221675.6</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>566147.36</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>178445</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-2.21</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3352.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-3.14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10.64</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>35.75</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>59.24</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>60.11</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>57.62</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-24.96</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-107.74</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>194731.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>289419.6</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>341561.2</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>568481.84</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-52141</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-35875.73082668789</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-30660.24445832073</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>194731</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>40.68</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>55.37</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-2.75</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>59.73999999999999</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>59.51</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>60.1</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>57.55</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-4.35</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-107.25</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>283328.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>437969.2</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>356514.8</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>570563.3</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>81454</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-36824.00107548192</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-22149.96022690379</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>283328</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-1.36</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>24.17</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>42.67</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4060.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-3.15</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>36.21</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7.01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>-1.86</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>55.93</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>67.23</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>-1.86</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>4.58</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>60.12</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>59.74</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>60.09</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>57.46</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-107.17</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>242218.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>465573.8</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>341803.5</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>579417.88</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>123770</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-39492.00850249613</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-18693.87703106157</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>242218</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>59.3</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3505.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-4.55</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>36.04</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>69.49</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>81.92</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>4.74</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>59.72000000000001</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>59.98</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>60.1</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>57.38</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>20.51</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-107.44</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>209656.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>452042.6</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>332281.8</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>596784.86</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>119760</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-43273.48695184787</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-8684.334000177623</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>209656</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>60.1</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-2.27</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8540.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-5.24</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>30.92</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14.74</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>-1.65</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>76.27</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>91.33</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>-1.58</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>4.83</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>59.14</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>60.09</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>60.08</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>57.31</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>9.30</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-107.82</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>814356.8199426112</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>517165.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>445047.0</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>339942.5</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>643736.64</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>105104</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-49562.42385215155</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>9413.953686805733</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>517165</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>61.7</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>22.98</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>57.16</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>58.14</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>60.07</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>60.07</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>162030.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>209836.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>209836.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>215755.9</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>550120.9</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>550120.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-38160.02218378661</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>162030</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>162030.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>57.23999999999999</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>58.29</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>60.05</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>60.05</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>199284.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>213119.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>213119.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>251269.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>555483.94</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>555483.9399999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-36671.78477886959</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>199284</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>199284.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>57.36</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>60.09</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>136228.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>212208.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>212208.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>325088.9</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>556448.64</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>556448.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-37227.52474402849</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>136228</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>136228.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>57.62</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>60.11</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>273475.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>241628.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>241628.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>353601.2</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>558552.82</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>558552.8199999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-29935.8845248259</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>273475</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>273475.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>58.17999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>60.16</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>60.16</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>278164.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>235377.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>235377.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>343709.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>560862.08</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>560862.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-33155.15262150689</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>278164</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>278164.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>58.38000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>59.01</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>60.14</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>178445.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>221675.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>221675.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>333361.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>566147.36</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>566147.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-37072.38730885455</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>178445</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>59.24</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>59.24</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>60.11</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>194731.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>289419.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>289419.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>341561.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>568481.84</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>568481.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-30660.24445832073</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>194731</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>194731.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>59.73999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>59.51</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>60.1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>283328.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>437969.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>437969.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>356514.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>570563.3</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>570563.3</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-22149.96022690379</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>283328</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>283328.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>60.12</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>59.74</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>60.09</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>242218.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>465573.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>465573.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>341803.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>579417.88</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>579417.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-18693.87703106157</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>242218</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>242218.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>59.72000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>59.98</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>60.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>209656.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>452042.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>452042.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>332281.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>596784.86</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>596784.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-8684.334000177623</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>209656</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>209656.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>59.14</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>60.09</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>60.08</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>60.08</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>517165.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>445047.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>445047</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>339942.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>643736.64</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>643736.64</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>9413.953686805733</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>517165</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>517165.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN2" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3484.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN3" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-32.85</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-32.85</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN5" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>58.9</v>
+        <v>58.66</v>
       </c>
       <c r="AN6" t="n">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-36.02</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.68</t>
+          <t>-109.54</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>235377.2</v>
+        <v>241628.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>343709.9</t>
+          <t>353601.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>560862.08</v>
+        <v>558552.8199999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-108332</t>
+          <t>-111972</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-35612.95810049239</t>
+          <t>-34739.56216577447</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-33155.15262150689</t>
+          <t>-29935.8845248259</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>59.01</v>
+        <v>58.9</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.14</v>
+        <v>60.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>221675.6</v>
+        <v>235377.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>566147.36</v>
+        <v>560862.08</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,141 +3594,141 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>813557.9312320916</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>221675.6</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>566147.36</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM8" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>814356.8199426112</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>289419.6</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>568481.84</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG8" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,72 +3908,72 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-2.14</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>59.51</v>
+        <v>59.24</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.1</v>
+        <v>60.11</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4110,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>437969.2</v>
+        <v>289419.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>570563.3</v>
+        <v>568481.84</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-22149.96022690379</t>
+          <t>-30660.24445832073</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,127 +4323,127 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-3.15</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-2.14</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>59.74</v>
+        <v>59.51</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.09</v>
+        <v>60.1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>465573.8</v>
+        <v>437969.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>579417.88</v>
+        <v>570563.3</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-18693.87703106157</t>
+          <t>-22149.96022690379</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,27 +4778,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>59.98</v>
+        <v>59.74</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.1</v>
+        <v>60.09</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,48 +4970,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>452042.6</v>
+        <v>465573.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>596784.86</v>
+        <v>579417.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-8684.334000177623</t>
+          <t>-18693.87703106157</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8540.0</t>
+          <t>3505.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>59.72000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>60.09</v>
+        <v>59.98</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.08</v>
+        <v>60.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.82</t>
+          <t>-107.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>814356.8199426112</t>
+          <t>813557.9312320916</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>445047</v>
+        <v>452042.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>339942.5</t>
+          <t>332281.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>643736.64</v>
+        <v>596784.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-49562.42385215155</t>
+          <t>-43273.48695184787</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>9413.953686805733</t>
+          <t>-8684.334000177623</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>517165.0</t>
+          <t>209656.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>58.08</v>
+        <v>58</v>
       </c>
       <c r="AN2" t="n">
-        <v>60.1</v>
+        <v>60.13</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>188434.4</v>
+        <v>179557.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>549840.7</v>
+        <v>551119.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3484.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN4" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-32.85</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN5" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-32.85</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN6" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>58.9</v>
+        <v>58.66</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-36.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.68</t>
+          <t>-109.54</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>235377.2</v>
+        <v>241628.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>343709.9</t>
+          <t>353601.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>560862.08</v>
+        <v>558552.8199999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-108332</t>
+          <t>-111972</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-35612.95810049239</t>
+          <t>-34739.56216577447</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-33155.15262150689</t>
+          <t>-29935.8845248259</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>59.01</v>
+        <v>58.9</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.14</v>
+        <v>60.16</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>221675.6</v>
+        <v>235377.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>566147.36</v>
+        <v>560862.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,141 +4024,141 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>812885.6566523606</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>221675.6</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>566147.36</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM9" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>813557.9312320916</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>289419.6</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>568481.84</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG9" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,72 +4338,72 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>59.51</v>
+        <v>59.24</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.1</v>
+        <v>60.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,48 +4540,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>437969.2</v>
+        <v>289419.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>570563.3</v>
+        <v>568481.84</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-22149.96022690379</t>
+          <t>-30660.24445832073</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,127 +4753,127 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-2.61</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>59.74</v>
+        <v>59.51</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.09</v>
+        <v>60.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>465573.8</v>
+        <v>437969.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>579417.88</v>
+        <v>570563.3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-18693.87703106157</t>
+          <t>-22149.96022690379</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3505.0</t>
+          <t>4060.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,22 +5208,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>55.93</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>67.23</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>59.72000000000001</t>
+          <t>60.12</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>59.98</v>
+        <v>59.74</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.1</v>
+        <v>60.09</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.44</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,48 +5400,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>813557.9312320916</t>
+          <t>812885.6566523606</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>452042.6</v>
+        <v>465573.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>332281.8</t>
+          <t>341803.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>596784.86</v>
+        <v>579417.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-43273.48695184787</t>
+          <t>-39492.00850249613</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-8684.334000177623</t>
+          <t>-18693.87703106157</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>209656.0</t>
+          <t>242218.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,63 +1014,63 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>58</v>
+        <v>57.92</v>
       </c>
       <c r="AN2" t="n">
-        <v>60.13</v>
+        <v>60.12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.82</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>179557.8</v>
+        <v>194330.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>210593.2</t>
+          <t>203269.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>551119.74</v>
+        <v>548208.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-31035</t>
+          <t>-8938</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-35417.44213935517</t>
+          <t>-34352.97788224091</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-31861.42593251113</t>
+          <t>-28498.42446811244</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>58.08</v>
+        <v>58</v>
       </c>
       <c r="AN3" t="n">
-        <v>60.1</v>
+        <v>60.13</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>188434.4</v>
+        <v>179557.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>549840.7</v>
+        <v>551119.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,42 +2173,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2826.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3484.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN5" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-32.85</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-32.85</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>58.9</v>
+        <v>58.66</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-36.02</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.68</t>
+          <t>-109.54</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>235377.2</v>
+        <v>241628.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>343709.9</t>
+          <t>353601.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>560862.08</v>
+        <v>558552.8199999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-108332</t>
+          <t>-111972</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-35612.95810049239</t>
+          <t>-34739.56216577447</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-33155.15262150689</t>
+          <t>-29935.8845248259</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>59.01</v>
+        <v>58.9</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.14</v>
+        <v>60.16</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>221675.6</v>
+        <v>235377.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>566147.36</v>
+        <v>560862.08</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,141 +4454,141 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>812174.5907142857</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>221675.6</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>566147.36</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM10" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>812885.6566523606</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>289419.6</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>568481.84</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG10" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,72 +4768,72 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>59.51</v>
+        <v>59.24</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.1</v>
+        <v>60.11</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,48 +4970,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>437969.2</v>
+        <v>289419.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>570563.3</v>
+        <v>568481.84</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-22149.96022690379</t>
+          <t>-30660.24445832073</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,127 +5183,127 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4870.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>-1.35</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4060.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-2.08</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>-1.86</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>67.23</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>60.12</t>
+          <t>59.73999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>59.74</v>
+        <v>59.51</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.09</v>
+        <v>60.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>812885.6566523606</t>
+          <t>812174.5907142857</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>465573.8</v>
+        <v>437969.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>341803.5</t>
+          <t>356514.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>579417.88</v>
+        <v>570563.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-39492.00850249613</t>
+          <t>-36824.00107548192</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-18693.87703106157</t>
+          <t>-22149.96022690379</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>242218.0</t>
+          <t>283328.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3642.0</t>
+          <t>2707.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>57.92</v>
+        <v>57.97</v>
       </c>
       <c r="AN2" t="n">
-        <v>60.12</v>
+        <v>60.08</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.82</t>
+          <t>-112.64</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>194330.8</v>
+        <v>185826.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>203269.7</t>
+          <t>199472.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>548208.92</v>
+        <v>509521.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-8938</t>
+          <t>-13646</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-34352.97788224091</t>
+          <t>-33595.86787440854</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-28498.42446811244</t>
+          <t>-29431.76283133053</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,63 +1444,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>58</v>
+        <v>57.92</v>
       </c>
       <c r="AN3" t="n">
-        <v>60.13</v>
+        <v>60.12</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.82</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>179557.8</v>
+        <v>194330.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>210593.2</t>
+          <t>203269.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>551119.74</v>
+        <v>548208.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-31035</t>
+          <t>-8938</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-35417.44213935517</t>
+          <t>-34352.97788224091</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-31861.42593251113</t>
+          <t>-28498.42446811244</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,84 +1768,84 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-14.74</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>-0.52</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-11.08</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>-4.07</t>
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>58.08</v>
+        <v>58</v>
       </c>
       <c r="AN4" t="n">
-        <v>60.1</v>
+        <v>60.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>188434.4</v>
+        <v>179557.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>549840.7</v>
+        <v>551119.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN5" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3484.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-32.85</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-32.85</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>58.9</v>
+        <v>58.66</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-36.02</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.68</t>
+          <t>-109.54</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>235377.2</v>
+        <v>241628.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>343709.9</t>
+          <t>353601.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>560862.08</v>
+        <v>558552.8199999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-108332</t>
+          <t>-111972</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-35612.95810049239</t>
+          <t>-34739.56216577447</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-33155.15262150689</t>
+          <t>-29935.8845248259</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>59.01</v>
+        <v>58.9</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.14</v>
+        <v>60.16</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>221675.6</v>
+        <v>235377.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>566147.36</v>
+        <v>560862.08</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,141 +4884,141 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/12/02</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>811351.4336661913</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>221675.6</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>566147.36</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM11" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>812174.5907142857</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>289419.6</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>568481.84</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG11" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4870.0</t>
+          <t>3352.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,72 +5198,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-15.27</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>59.73999999999999</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>59.51</v>
+        <v>59.24</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.1</v>
+        <v>60.11</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-24.96</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,58 +5390,58 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-107.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>812174.5907142857</t>
+          <t>811351.4336661913</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>437969.2</v>
+        <v>289419.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>356514.8</t>
+          <t>341561.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>570563.3</v>
+        <v>568481.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>81454</t>
+          <t>-52141</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-36824.00107548192</t>
+          <t>-35875.73082668789</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-22149.96022690379</t>
+          <t>-30660.24445832073</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>283328.0</t>
+          <t>194731.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2707.0</t>
+          <t>5264.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,68 +1014,68 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>57.97</v>
+        <v>58.02</v>
       </c>
       <c r="AN2" t="n">
-        <v>60.08</v>
+        <v>60.01</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>58.45</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.64</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>811351.4336661913</t>
+          <t>810837.517094017</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>185826.2</v>
+        <v>213497.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>199472.7</t>
+          <t>211667.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>509521.28</v>
+        <v>500099.3</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-13646</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-33595.86787440854</t>
+          <t>-31285.31598831491</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-29431.76283133053</t>
+          <t>-18577.28061479991</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,42 +1313,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2707.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>-1.03</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3642.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>57.2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.96</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>57.92</v>
+        <v>57.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>60.12</v>
+        <v>60.08</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.82</t>
+          <t>-112.64</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>811351.4336661913</t>
+          <t>810837.517094017</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>194330.8</v>
+        <v>185826.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>203269.7</t>
+          <t>199472.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>548208.92</v>
+        <v>509521.28</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-8938</t>
+          <t>-13646</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-34352.97788224091</t>
+          <t>-33595.86787440854</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-28498.42446811244</t>
+          <t>-29431.76283133053</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,63 +1874,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>58</v>
+        <v>57.92</v>
       </c>
       <c r="AN4" t="n">
-        <v>60.13</v>
+        <v>60.12</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.82</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>811351.4336661913</t>
+          <t>810837.517094017</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>179557.8</v>
+        <v>194330.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>210593.2</t>
+          <t>203269.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>551119.74</v>
+        <v>548208.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-31035</t>
+          <t>-8938</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-35417.44213935517</t>
+          <t>-34352.97788224091</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-31861.42593251113</t>
+          <t>-28498.42446811244</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>58.08</v>
+        <v>58</v>
       </c>
       <c r="AN5" t="n">
-        <v>60.1</v>
+        <v>60.13</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>811351.4336661913</t>
+          <t>810837.517094017</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>188434.4</v>
+        <v>179557.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>549840.7</v>
+        <v>551119.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN6" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>811351.4336661913</t>
+          <t>810837.517094017</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3484.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-32.85</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>811351.4336661913</t>
+          <t>810837.517094017</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-32.85</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>811351.4336661913</t>
+          <t>810837.517094017</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>811351.4336661913</t>
+          <t>810837.517094017</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>58.9</v>
+        <v>58.66</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-36.02</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.68</t>
+          <t>-109.54</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>811351.4336661913</t>
+          <t>810837.517094017</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>235377.2</v>
+        <v>241628.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>343709.9</t>
+          <t>353601.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>560862.08</v>
+        <v>558552.8199999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-108332</t>
+          <t>-111972</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-35612.95810049239</t>
+          <t>-34739.56216577447</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-33155.15262150689</t>
+          <t>-29935.8845248259</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>59.01</v>
+        <v>58.9</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.14</v>
+        <v>60.16</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>811351.4336661913</t>
+          <t>810837.517094017</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>221675.6</v>
+        <v>235377.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>566147.36</v>
+        <v>560862.08</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3352.0</t>
+          <t>3082.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-33.50</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,141 +5314,141 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>58.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-30.25</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-108.37</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/12/02</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>810837.517094017</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>221675.6</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>333361.3</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>566147.36</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-111685</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-36059.8318239443</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-37072.38730885455</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>178445.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="AM12" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-24.96</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-107.74</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>811351.4336661913</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>289419.6</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>341561.2</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>568481.84</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-52141</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-35875.73082668789</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-30660.24445832073</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>194731.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
       <c r="BG12" t="inlineStr">
         <is>
           <t>2025/08/29</t>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -883,109 +883,109 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2826.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.36</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>-1.89</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5264.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>-4.07</t>
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,75 +1014,75 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM2" t="n">
         <v>58.02</v>
       </c>
       <c r="AN2" t="n">
-        <v>60.01</v>
+        <v>59.93</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.45</t>
+          <t>58.52</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.67</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>5.31</t>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>810837.517094017</t>
+          <t>810026.5348506402</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>213497.8</v>
+        <v>211362.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>211667.0</t>
+          <t>199898.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>500099.3</v>
+        <v>488500.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-31285.31598831491</t>
+          <t>-29704.18445901392</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-18577.28061479991</t>
+          <t>-21007.96104785847</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2707.0</t>
+          <t>5264.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,68 +1444,68 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>57.97</v>
+        <v>58.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>60.08</v>
+        <v>60.01</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>58.45</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.64</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>810837.517094017</t>
+          <t>810026.5348506402</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>185826.2</v>
+        <v>213497.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>199472.7</t>
+          <t>211667.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>509521.28</v>
+        <v>500099.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-13646</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-33595.86787440854</t>
+          <t>-31285.31598831491</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-29431.76283133053</t>
+          <t>-18577.28061479991</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3642.0</t>
+          <t>2707.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>57.92</v>
+        <v>57.97</v>
       </c>
       <c r="AN4" t="n">
-        <v>60.12</v>
+        <v>60.08</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.82</t>
+          <t>-112.64</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>810837.517094017</t>
+          <t>810026.5348506402</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>194330.8</v>
+        <v>185826.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>203269.7</t>
+          <t>199472.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>548208.92</v>
+        <v>509521.28</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-8938</t>
+          <t>-13646</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-34352.97788224091</t>
+          <t>-33595.86787440854</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-28498.42446811244</t>
+          <t>-29431.76283133053</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,63 +2304,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>58</v>
+        <v>57.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>60.13</v>
+        <v>60.12</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.82</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>810837.517094017</t>
+          <t>810026.5348506402</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>179557.8</v>
+        <v>194330.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>210593.2</t>
+          <t>203269.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>551119.74</v>
+        <v>548208.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-31035</t>
+          <t>-8938</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-35417.44213935517</t>
+          <t>-34352.97788224091</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-31861.42593251113</t>
+          <t>-28498.42446811244</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>58.08</v>
+        <v>58</v>
       </c>
       <c r="AN6" t="n">
-        <v>60.1</v>
+        <v>60.13</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>810837.517094017</t>
+          <t>810026.5348506402</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>188434.4</v>
+        <v>179557.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>549840.7</v>
+        <v>551119.74</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3063,79 +3063,79 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>-1.36</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>-1.03</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-2.74</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>-4.07</t>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>810837.517094017</t>
+          <t>810026.5348506402</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3484.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-32.85</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>810837.517094017</t>
+          <t>810026.5348506402</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-32.85</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>810837.517094017</t>
+          <t>810026.5348506402</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>810837.517094017</t>
+          <t>810026.5348506402</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>58.9</v>
+        <v>58.66</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-36.02</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.68</t>
+          <t>-109.54</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>810837.517094017</t>
+          <t>810026.5348506402</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>235377.2</v>
+        <v>241628.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>343709.9</t>
+          <t>353601.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>560862.08</v>
+        <v>558552.8199999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-108332</t>
+          <t>-111972</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-35612.95810049239</t>
+          <t>-34739.56216577447</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-33155.15262150689</t>
+          <t>-29935.8845248259</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3082.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.50</t>
+          <t>-31.52</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>58.38000000000001</t>
+          <t>58.17999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>59.01</v>
+        <v>58.9</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.14</v>
+        <v>60.16</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-30.25</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.37</t>
+          <t>-108.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>810837.517094017</t>
+          <t>810026.5348506402</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>221675.6</v>
+        <v>235377.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>333361.3</t>
+          <t>343709.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>566147.36</v>
+        <v>560862.08</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-111685</t>
+          <t>-108332</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-36059.8318239443</t>
+          <t>-35612.95810049239</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-37072.38730885455</t>
+          <t>-33155.15262150689</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>178445.0</t>
+          <t>278164.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -871,11 +871,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>1785</t>
@@ -883,12 +879,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2635.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +909,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +989,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1010,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,59 +1025,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>40.02</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-1.53</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AM2" t="n">
         <v>58.02</v>
       </c>
       <c r="AN2" t="n">
-        <v>59.93</v>
+        <v>59.79</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.52</t>
+          <t>58.57</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.66</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1078,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.58</t>
+          <t>-112.50</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1088,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>810026.5348506402</t>
+          <t>809195.9616477273</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>160478.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>211362.4</v>
+        <v>195584.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>199898.4</t>
+          <t>187571.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>488500.72</v>
+        <v>459165.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-29704.18445901392</t>
+          <t>-28665.83889990455</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-21007.96104785847</t>
+          <t>-22954.93832480302</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>160478.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1189,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1229,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1254,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1301,11 +1289,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>1785</t>
@@ -1313,109 +1297,109 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2826.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.74</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>-1.89</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>5264.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>-4.07</t>
@@ -1423,17 +1407,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1428,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>43.75</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
+          <t>40.02</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-1.25</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>58.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>60.01</v>
+        <v>59.93</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.45</t>
+          <t>58.52</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.67</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1496,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.58</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1506,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>810026.5348506402</t>
+          <t>809195.9616477273</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>213497.8</v>
+        <v>211362.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>211667.0</t>
+          <t>199898.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>500099.3</v>
+        <v>488500.72</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-31285.31598831491</t>
+          <t>-29704.18445901392</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-18577.28061479991</t>
+          <t>-21007.96104785847</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1562,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1607,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1647,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1672,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1731,11 +1707,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>1785</t>
@@ -1743,12 +1715,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2707.0</t>
+          <t>5264.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1730,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1740,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1815,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1825,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1846,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>53.85</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-0.81</t>
-        </is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-1.07</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>57.97</v>
+        <v>58.02</v>
       </c>
       <c r="AN4" t="n">
-        <v>60.08</v>
+        <v>60.01</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>58.45</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>5.58</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.67</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1914,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.64</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1924,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>810026.5348506402</t>
+          <t>809195.9616477273</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>185826.2</v>
+        <v>213497.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>199472.7</t>
+          <t>211667.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>509521.28</v>
+        <v>500099.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-13646</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-33595.86787440854</t>
+          <t>-31285.31598831491</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-29431.76283133053</t>
+          <t>-18577.28061479991</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1980,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2025,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2065,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2090,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2161,11 +2125,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>1785</t>
@@ -2173,12 +2133,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3642.0</t>
+          <t>2707.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2148,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2158,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2233,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2243,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2264,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
+          <t>53.85</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>57.92</v>
+        <v>57.97</v>
       </c>
       <c r="AN5" t="n">
-        <v>60.12</v>
+        <v>60.08</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.26</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.70</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
+          <t>5.58</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.67</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2332,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.82</t>
+          <t>-112.64</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2342,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>810026.5348506402</t>
+          <t>809195.9616477273</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>194330.8</v>
+        <v>185826.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>203269.7</t>
+          <t>199472.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>548208.92</v>
+        <v>509521.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-8938</t>
+          <t>-13646</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-34352.97788224091</t>
+          <t>-33595.86787440854</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-28498.42446811244</t>
+          <t>-29431.76283133053</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2398,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2443,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2453,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2483,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2508,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2555,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2570,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2580,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2655,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2665,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2686,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>49.08</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-1.34</t>
-        </is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-1.06</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>58</v>
+        <v>57.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>60.13</v>
+        <v>60.12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-4.05</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.70</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
+          <t>-2.26</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.68</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2754,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.82</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2764,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>810026.5348506402</t>
+          <t>809195.9616477273</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>179557.8</v>
+        <v>194330.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>210593.2</t>
+          <t>203269.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>551119.74</v>
+        <v>548208.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-31035</t>
+          <t>-8938</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-35417.44213935517</t>
+          <t>-34352.97788224091</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-31861.42593251113</t>
+          <t>-28498.42446811244</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2820,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2875,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2905,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2930,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3038,7 +2982,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +2992,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3002,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3077,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3087,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3108,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>34.13</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-2.02</t>
-        </is>
+          <t>49.08</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-1.34</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>58.08</v>
+        <v>58</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.1</v>
+        <v>60.13</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-14.26</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
+          <t>-4.05</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.68</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3176,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3186,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>810026.5348506402</t>
+          <t>809195.9616477273</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>188434.4</v>
+        <v>179557.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>549840.7</v>
+        <v>551119.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3242,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3287,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3297,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3327,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,12 +3352,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3367,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3399,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3414,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3424,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3499,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3509,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3530,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
+          <t>34.13</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-2.02</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-24.14</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
+          <t>-14.26</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.67</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3598,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3608,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>810026.5348506402</t>
+          <t>809195.9616477273</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3664,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3709,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3749,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3774,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3821,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3484.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3836,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3846,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3921,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3931,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3952,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.56</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-1.80</t>
-        </is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-1.69</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-32.85</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.81</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
+          <t>-24.14</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.65</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4020,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4030,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>810026.5348506402</t>
+          <t>809195.9616477273</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4086,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4131,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4171,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4196,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4243,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4353,12 +4273,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4433,17 +4353,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4374,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>16.11</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
+          <t>10.56</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-1.8</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-36.35</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
+          <t>-32.85</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.61</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4442,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4452,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>810026.5348506402</t>
+          <t>809195.9616477273</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4641,7 +4553,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4681,7 +4593,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,17 +4618,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4753,12 +4665,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4680,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4690,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4765,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4775,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4796,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>15.46</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-1.76</t>
-        </is>
+          <t>16.11</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-1.88</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-36.02</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
+          <t>-36.35</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4864,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4874,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>810026.5348506402</t>
+          <t>809195.9616477273</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4930,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4975,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +4985,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5015,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5040,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5087,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>4791.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5102,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5112,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-31.52</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5187,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5197,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,74 +5218,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-1.21</t>
-        </is>
+          <t>15.46</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.76</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>58.17999999999999</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>58.9</v>
+        <v>58.66</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.48</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
+          <t>-36.02</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.51</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5286,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.68</t>
+          <t>-109.54</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5296,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>810026.5348506402</t>
+          <t>809195.9616477273</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>235377.2</v>
+        <v>241628.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>343709.9</t>
+          <t>353601.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>560862.08</v>
+        <v>558552.8199999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-108332</t>
+          <t>-111972</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-35612.95810049239</t>
+          <t>-34739.56216577447</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-33155.15262150689</t>
+          <t>-29935.8845248259</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>278164.0</t>
+          <t>273475.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5352,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5397,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5407,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5437,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5462,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>1785</t>
@@ -879,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6619.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2635.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -924,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -979,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -989,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1010,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.25</v>
+        <v>2.88</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.53</v>
+        <v>-0.77</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>58.02</v>
+        <v>57.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>59.79</v>
+        <v>59.72</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.57</t>
+          <t>58.65</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.65</v>
+        <v>-0.45</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.66</v>
+        <v>-0.62</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.50</t>
+          <t>-111.71</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1088,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>809195.9616477273</t>
+          <t>808872.6872340427</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>150202.0</t>
+          <t>387525.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>195584.4</v>
+        <v>231070.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>187571.1</t>
+          <t>212700.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>459165.6</v>
+        <v>426509.1</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-28665.83889990455</t>
+          <t>-25170.28275538756</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-22954.93832480302</t>
+          <t>-5944.723960544128</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>150202.0</t>
+          <t>387525.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1169,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1189,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1214,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1229,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1259,17 +1263,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1289,7 +1293,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>1785</t>
@@ -1297,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2635.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1322,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1342,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1407,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1428,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1443,52 +1451,52 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.52</v>
+        <v>-0.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.25</v>
+        <v>-1.53</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>58.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>59.93</v>
+        <v>59.79</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.52</t>
+          <t>58.57</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AQ3" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="AR3" t="n">
         <v>-0.66</v>
       </c>
-      <c r="AR3" t="n">
-        <v>-0.67</v>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>5.31</t>
@@ -1496,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.58</t>
+          <t>-112.50</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1506,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>809195.9616477273</t>
+          <t>808872.6872340427</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>160478.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>211362.4</v>
+        <v>195584.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>199898.4</t>
+          <t>187571.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>488500.72</v>
+        <v>459165.6</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-29704.18445901392</t>
+          <t>-28665.83889990455</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-21007.96104785847</t>
+          <t>-22954.93832480302</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>160478.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1587,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1607,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1622,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1632,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1647,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1672,17 +1680,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1707,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>1785</t>
@@ -1715,109 +1727,109 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2826.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>-1.89</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5264.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.74</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>-4.07</t>
@@ -1825,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1846,63 +1858,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-1.22</v>
+        <v>-0.52</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.07</v>
+        <v>-1.25</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM4" t="n">
         <v>58.02</v>
       </c>
       <c r="AN4" t="n">
-        <v>60.01</v>
+        <v>59.93</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.45</t>
+          <t>58.52</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AR4" t="n">
         <v>-0.67</v>
@@ -1914,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1924,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>809195.9616477273</t>
+          <t>808872.6872340427</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>213497.8</v>
+        <v>211362.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>211667.0</t>
+          <t>199898.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>500099.3</v>
+        <v>488500.72</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-31285.31598831491</t>
+          <t>-29704.18445901392</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-18577.28061479991</t>
+          <t>-21007.96104785847</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1980,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2005,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2025,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2050,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2065,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2090,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2125,7 +2137,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>1785</t>
@@ -2133,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2707.0</t>
+          <t>5264.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2148,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2158,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2178,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2233,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2243,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2264,63 +2280,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.52</v>
+        <v>-1.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.07</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>57.97</v>
+        <v>58.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>60.08</v>
+        <v>60.01</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>58.45</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.63</v>
+        <v>-0.67</v>
       </c>
       <c r="AR5" t="n">
         <v>-0.67</v>
@@ -2332,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.64</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2342,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>809195.9616477273</t>
+          <t>808872.6872340427</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>185826.2</v>
+        <v>213497.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>199472.7</t>
+          <t>211667.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>509521.28</v>
+        <v>500099.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-13646</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-33595.86787440854</t>
+          <t>-31285.31598831491</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-29431.76283133053</t>
+          <t>-18577.28061479991</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2398,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2423,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2443,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2468,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2483,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2508,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2545,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2555,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3642.0</t>
+          <t>2707.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2570,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2580,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2600,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2655,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2665,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2686,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.17</v>
+        <v>0.52</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.06</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>57.92</v>
+        <v>57.97</v>
       </c>
       <c r="AN6" t="n">
-        <v>60.12</v>
+        <v>60.08</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.7</v>
+        <v>-0.63</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2754,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.82</t>
+          <t>-112.64</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2764,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>809195.9616477273</t>
+          <t>808872.6872340427</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>194330.8</v>
+        <v>185826.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>203269.7</t>
+          <t>199472.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>548208.92</v>
+        <v>509521.28</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-8938</t>
+          <t>-13646</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-34352.97788224091</t>
+          <t>-33595.86787440854</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-28498.42446811244</t>
+          <t>-29431.76283133053</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2820,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2845,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2865,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2875,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2890,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2905,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2930,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2977,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2992,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3002,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3022,7 +3038,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3077,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3087,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3108,59 +3124,59 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.01</v>
+        <v>-0.17</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.34</v>
+        <v>-1.06</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>58</v>
+        <v>57.92</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.13</v>
+        <v>60.12</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AQ7" t="n">
@@ -3176,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.82</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3186,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>809195.9616477273</t>
+          <t>808872.6872340427</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>179557.8</v>
+        <v>194330.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>210593.2</t>
+          <t>203269.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>551119.74</v>
+        <v>548208.92</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-31035</t>
+          <t>-8938</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-35417.44213935517</t>
+          <t>-34352.97788224091</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-31861.42593251113</t>
+          <t>-28498.42446811244</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3242,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3267,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3297,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3312,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3327,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3352,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3404,7 +3420,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3414,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3424,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3444,7 +3460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3499,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3509,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3530,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.02</v>
+        <v>-1.34</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>58.08</v>
+        <v>58</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.1</v>
+        <v>60.13</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.77</v>
+        <v>-0.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.67</v>
+        <v>-0.68</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3598,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3608,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>809195.9616477273</t>
+          <t>808872.6872340427</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>188434.4</v>
+        <v>179557.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>549840.7</v>
+        <v>551119.74</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3664,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3689,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3709,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3719,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3734,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3749,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3774,12 +3790,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3789,7 +3805,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3821,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3836,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3846,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3866,7 +3882,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3921,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3931,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3952,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.69</v>
+        <v>-2.02</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.8</v>
+        <v>-0.77</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.65</v>
+        <v>-0.67</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4020,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4030,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>809195.9616477273</t>
+          <t>808872.6872340427</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4086,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4111,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4131,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4156,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4171,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4196,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4243,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3484.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4258,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4268,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4288,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4343,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4353,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4374,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.77</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.8</v>
+        <v>-1.69</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.23999999999999</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>58.29</v>
+        <v>58.14</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.05</v>
+        <v>60.07</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-32.85</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.61</v>
+        <v>-0.65</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4442,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4452,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>809195.9616477273</t>
+          <t>808872.6872340427</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>213119.2</v>
+        <v>209836.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>555483.9399999999</v>
+        <v>550120.9</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4508,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4533,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4553,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4563,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4578,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4593,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4618,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4665,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>3484.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4690,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4710,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4775,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4796,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.98</v>
+        <v>-0.77</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.88</v>
+        <v>-1.8</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.23999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>58.46</v>
+        <v>58.29</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.09</v>
+        <v>60.05</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-32.85</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.76</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.61</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4864,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-111.43</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4874,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>809195.9616477273</t>
+          <t>808872.6872340427</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>212208.6</v>
+        <v>213119.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>251269.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>556448.64</v>
+        <v>555483.9399999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-38150</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35360.70396850856</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-36671.78477886959</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>199284.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4955,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4975,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4990,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5000,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5015,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5040,17 +5056,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5087,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4791.0</t>
+          <t>2408.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5102,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5112,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-34.72</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5132,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5187,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5197,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5218,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-2.46</v>
+        <v>-0.98</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.76</v>
+        <v>-1.88</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.11</v>
+        <v>60.09</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-36.02</t>
+          <t>-36.35</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.76</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5286,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.54</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5296,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>809195.9616477273</t>
+          <t>808872.6872340427</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>241628.6</v>
+        <v>212208.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>353601.2</t>
+          <t>325088.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>558552.8199999999</v>
+        <v>556448.64</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-111972</t>
+          <t>-112880</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-34739.56216577447</t>
+          <t>-35122.32563935201</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-29935.8845248259</t>
+          <t>-37227.52474402849</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>273475.0</t>
+          <t>136228.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5352,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5377,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5397,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5407,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5422,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5437,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5462,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6619.0</t>
+          <t>30630.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>2.88</v>
+        <v>7.41</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.77</v>
+        <v>2.26</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>57.98</v>
+        <v>58.08</v>
       </c>
       <c r="AN2" t="n">
-        <v>59.72</v>
+        <v>59.68</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>58.86</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>163.23</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.45</v>
+        <v>0.24</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.62</v>
+        <v>-0.39</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.71</t>
+          <t>-107.28</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>808872.6872340427</t>
+          <t>812030.3550212164</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>387525.0</t>
+          <t>1939088.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>231070.8</v>
+        <v>653003.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>212700.8</t>
+          <t>433250.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>426509.1</v>
+        <v>423371.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>219752</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-25170.28275538756</t>
+          <t>7107.715248879902</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-5944.723960544128</t>
+          <t>142924.5545464109</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>387525.0</t>
+          <t>1939088.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2635.0</t>
+          <t>10381.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>21.41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,201 +1436,201 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.25</v>
+        <v>3.48</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.53</v>
+        <v>0.13</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.98</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>58.02</v>
+        <v>57.91</v>
       </c>
       <c r="AN3" t="n">
-        <v>59.79</v>
+        <v>59.65</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.57</t>
+          <t>58.74</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
+          <t>57.05</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-110.25</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/12/02</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>812030.3550212164</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>627723.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>325263.2</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>255544.7</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>399545.28</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>69718</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-17586.25553248937</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>24125.89419345069</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>627723.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
           <t>2.61</t>
         </is>
       </c>
-      <c r="AQ3" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-112.50</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>808872.6872340427</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>150202.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>195584.4</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>187571.1</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>459165.6</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>8013</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-28665.83889990455</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-22954.93832480302</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>150202.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>6619.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,266 +1858,266 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.52</v>
+        <v>2.88</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.25</v>
+        <v>-0.77</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>57.54</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>58.65</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>27.03</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-111.71</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/12/02</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>812030.3550212164</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>387525.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>231070.8</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>212700.8</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>426509.1</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>18370</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-25170.28275538756</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-5944.723960544128</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>387525.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>27.15</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>46.45</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>38025</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="AM4" t="n">
-        <v>58.02</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>59.93</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>58.52</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-112.58</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>808872.6872340427</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>160478.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>211362.4</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>199898.4</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>488500.72</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>11464</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-29704.18445901392</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-21007.96104785847</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>160478.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>3.38</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>25.19</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>46.32</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>35283</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,109 +2149,109 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2635.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10.66</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>-1.89</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5264.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>-4.07</t>
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-1.22</v>
+        <v>-0.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.07</v>
+        <v>-1.53</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AM5" t="n">
         <v>58.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>60.01</v>
+        <v>59.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.45</t>
+          <t>58.57</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.67</v>
+        <v>-0.65</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.50</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>808872.6872340427</t>
+          <t>812030.3550212164</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>213497.8</v>
+        <v>195584.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>211667.0</t>
+          <t>187571.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>500099.3</v>
+        <v>459165.6</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-31285.31598831491</t>
+          <t>-28665.83889990455</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-18577.28061479991</t>
+          <t>-22954.93832480302</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2707.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,63 +2702,63 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.52</v>
+        <v>-0.52</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.25</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>57.97</v>
+        <v>58.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>60.08</v>
+        <v>59.93</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>58.52</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.63</v>
+        <v>-0.66</v>
       </c>
       <c r="AR6" t="n">
         <v>-0.67</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.64</t>
+          <t>-112.58</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>808872.6872340427</t>
+          <t>812030.3550212164</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>185826.2</v>
+        <v>211362.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>199472.7</t>
+          <t>199898.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>509521.28</v>
+        <v>488500.72</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-13646</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-33595.86787440854</t>
+          <t>-29704.18445901392</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-29431.76283133053</t>
+          <t>-21007.96104785847</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3642.0</t>
+          <t>5264.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.17</v>
+        <v>-1.22</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.06</v>
+        <v>-1.07</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>57.92</v>
+        <v>58.02</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.12</v>
+        <v>60.01</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.45</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.7</v>
+        <v>-0.67</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.82</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>808872.6872340427</t>
+          <t>812030.3550212164</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>194330.8</v>
+        <v>213497.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>203269.7</t>
+          <t>211667.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>548208.92</v>
+        <v>500099.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-8938</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-34352.97788224091</t>
+          <t>-31285.31598831491</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-28498.42446811244</t>
+          <t>-18577.28061479991</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3373,17 +3373,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>2707.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.01</v>
+        <v>0.52</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.34</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>58</v>
+        <v>57.97</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.13</v>
+        <v>60.08</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.7</v>
+        <v>-0.63</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.64</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>808872.6872340427</t>
+          <t>812030.3550212164</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>179557.8</v>
+        <v>185826.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>210593.2</t>
+          <t>199472.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>551119.74</v>
+        <v>509521.28</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-31035</t>
+          <t>-13646</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-35417.44213935517</t>
+          <t>-33595.86787440854</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-31861.42593251113</t>
+          <t>-29431.76283133053</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>38.46</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>34.13</t>
-        </is>
-      </c>
       <c r="AH9" t="n">
-        <v>1.05</v>
+        <v>-0.17</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.02</v>
+        <v>-1.06</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>58.08</v>
+        <v>57.92</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.1</v>
+        <v>60.12</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.77</v>
+        <v>-0.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.67</v>
+        <v>-0.68</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.82</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>808872.6872340427</t>
+          <t>812030.3550212164</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>188434.4</v>
+        <v>194330.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>203269.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>549840.7</v>
+        <v>548208.92</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-8938</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-34352.97788224091</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-28498.42446811244</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.69</v>
+        <v>-1.34</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>58.14</v>
+        <v>58</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.07</v>
+        <v>60.13</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.65</v>
+        <v>-0.68</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>808872.6872340427</t>
+          <t>812030.3550212164</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>209836.2</v>
+        <v>179557.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>550120.9</v>
+        <v>551119.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3484.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-3.37</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>56.9</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>58.08</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>58.16</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-14.26</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
         <v>-0.77</v>
       </c>
-      <c r="AI11" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>57.23999999999999</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>60.05</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>57.99</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-32.85</t>
-        </is>
-      </c>
-      <c r="AQ11" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
       <c r="AR11" t="n">
-        <v>-0.61</v>
+        <v>-0.67</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.43</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>808872.6872340427</t>
+          <t>812030.3550212164</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>213119.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>251269.4</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>555483.9399999999</v>
+        <v>549840.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-38150</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-35360.70396850856</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-36671.78477886959</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>199284.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2408.0</t>
+          <t>2826.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.72</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.98</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.88</v>
+        <v>-1.69</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>58.46</v>
+        <v>58.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.09</v>
+        <v>60.07</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-24.14</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.76</v>
+        <v>-0.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.65</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.17</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>808872.6872340427</t>
+          <t>812030.3550212164</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>212208.6</v>
+        <v>209836.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>325088.9</t>
+          <t>215755.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>556448.64</v>
+        <v>550120.9</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-112880</t>
+          <t>-5919</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-35122.32563935201</t>
+          <t>-35791.36830932057</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-37227.52474402849</t>
+          <t>-38160.02218378661</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>136228.0</t>
+          <t>162030.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30630.0</t>
+          <t>17140.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>59.80</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>35.36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.77</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.59</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>7.41</v>
+        <v>4.61</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.26</v>
+        <v>4.17</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>58.08</v>
+        <v>58.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>59.68</v>
+        <v>59.72</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>163.23</t>
+          <t>410.51</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.24</v>
+        <v>0.59</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.39</v>
+        <v>-0.19</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.28</t>
+          <t>-103.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>812030.3550212164</t>
+          <t>813205.7563559322</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1939088.0</t>
+          <t>1096143.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>653003.2</v>
+        <v>840136.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>433250.5</t>
+          <t>525749.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>423371.84</v>
+        <v>433831.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>219752</t>
+          <t>314386</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>7107.715248879902</t>
+          <t>30520.31719979418</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>142924.5545464109</t>
+          <t>159289.6279298227</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1939088.0</t>
+          <t>1096143.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10381.0</t>
+          <t>30630.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1451,51 +1451,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>3.48</v>
+        <v>7.41</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.13</v>
+        <v>2.26</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>57.98</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>57.91</v>
+        <v>58.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>59.65</v>
+        <v>59.68</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.74</t>
+          <t>58.86</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>163.23</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.23</v>
+        <v>0.24</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.54</v>
+        <v>-0.39</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.25</t>
+          <t>-107.28</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>812030.3550212164</t>
+          <t>813205.7563559322</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>627723.0</t>
+          <t>1939088.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>325263.2</v>
+        <v>653003.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>255544.7</t>
+          <t>433250.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>399545.28</v>
+        <v>423371.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>219752</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-17586.25553248937</t>
+          <t>7107.715248879902</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>24125.89419345069</t>
+          <t>142924.5545464109</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>627723.0</t>
+          <t>1939088.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6619.0</t>
+          <t>10381.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>21.41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1873,51 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>2.88</v>
+        <v>3.48</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.77</v>
+        <v>0.13</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.98</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>57.98</v>
+        <v>57.91</v>
       </c>
       <c r="AN4" t="n">
-        <v>59.72</v>
+        <v>59.65</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>58.74</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.45</v>
+        <v>-0.23</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.62</v>
+        <v>-0.54</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.71</t>
+          <t>-110.25</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>812030.3550212164</t>
+          <t>813205.7563559322</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>387525.0</t>
+          <t>627723.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>231070.8</v>
+        <v>325263.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>212700.8</t>
+          <t>255544.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>426509.1</v>
+        <v>399545.28</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>69718</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-25170.28275538756</t>
+          <t>-17586.25553248937</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-5944.723960544128</t>
+          <t>24125.89419345069</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>387525.0</t>
+          <t>627723.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2635.0</t>
+          <t>6619.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.25</v>
+        <v>2.88</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.53</v>
+        <v>-0.77</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>58.02</v>
+        <v>57.98</v>
       </c>
       <c r="AN5" t="n">
-        <v>59.79</v>
+        <v>59.72</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.57</t>
+          <t>58.65</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.65</v>
+        <v>-0.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.66</v>
+        <v>-0.62</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.50</t>
+          <t>-111.71</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>812030.3550212164</t>
+          <t>813205.7563559322</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>150202.0</t>
+          <t>387525.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>195584.4</v>
+        <v>231070.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>187571.1</t>
+          <t>212700.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>459165.6</v>
+        <v>426509.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-28665.83889990455</t>
+          <t>-25170.28275538756</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-22954.93832480302</t>
+          <t>-5944.723960544128</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>150202.0</t>
+          <t>387525.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2635.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2717,52 +2717,52 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.52</v>
+        <v>-0.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.25</v>
+        <v>-1.53</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AM6" t="n">
         <v>58.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>59.93</v>
+        <v>59.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.52</t>
+          <t>58.57</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AQ6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="AR6" t="n">
         <v>-0.66</v>
       </c>
-      <c r="AR6" t="n">
-        <v>-0.67</v>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>5.31</t>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.58</t>
+          <t>-112.50</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>812030.3550212164</t>
+          <t>813205.7563559322</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>160478.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>211362.4</v>
+        <v>195584.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>199898.4</t>
+          <t>187571.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>488500.72</v>
+        <v>459165.6</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-29704.18445901392</t>
+          <t>-28665.83889990455</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-21007.96104785847</t>
+          <t>-22954.93832480302</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>160478.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -2993,109 +2993,109 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2826.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>10.24</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>-1.89</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>5264.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>11.13</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>-4.07</t>
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,63 +3124,63 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-1.22</v>
+        <v>-0.52</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.07</v>
+        <v>-1.25</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
         <v>58.02</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.01</v>
+        <v>59.93</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.45</t>
+          <t>58.52</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AR7" t="n">
         <v>-0.67</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.58</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>812030.3550212164</t>
+          <t>813205.7563559322</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>213497.8</v>
+        <v>211362.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>211667.0</t>
+          <t>199898.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>500099.3</v>
+        <v>488500.72</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-31285.31598831491</t>
+          <t>-29704.18445901392</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-18577.28061479991</t>
+          <t>-21007.96104785847</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2707.0</t>
+          <t>5264.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,63 +3546,63 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.52</v>
+        <v>-1.22</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.07</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>57.97</v>
+        <v>58.02</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.08</v>
+        <v>60.01</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>58.45</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.63</v>
+        <v>-0.67</v>
       </c>
       <c r="AR8" t="n">
         <v>-0.67</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.64</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>812030.3550212164</t>
+          <t>813205.7563559322</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>185826.2</v>
+        <v>213497.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>199472.7</t>
+          <t>211667.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>509521.28</v>
+        <v>500099.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-13646</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-33595.86787440854</t>
+          <t>-31285.31598831491</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-29431.76283133053</t>
+          <t>-18577.28061479991</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3642.0</t>
+          <t>2707.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.17</v>
+        <v>0.52</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.06</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>57.92</v>
+        <v>57.97</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.12</v>
+        <v>60.08</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.7</v>
+        <v>-0.63</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.82</t>
+          <t>-112.64</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>812030.3550212164</t>
+          <t>813205.7563559322</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>194330.8</v>
+        <v>185826.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>203269.7</t>
+          <t>199472.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>548208.92</v>
+        <v>509521.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-8938</t>
+          <t>-13646</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-34352.97788224091</t>
+          <t>-33595.86787440854</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-28498.42446811244</t>
+          <t>-29431.76283133053</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,59 +4390,59 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.01</v>
+        <v>-0.17</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.34</v>
+        <v>-1.06</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>58</v>
+        <v>57.92</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.13</v>
+        <v>60.12</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AQ10" t="n">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.82</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>812030.3550212164</t>
+          <t>813205.7563559322</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>179557.8</v>
+        <v>194330.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>210593.2</t>
+          <t>203269.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>551119.74</v>
+        <v>548208.92</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-31035</t>
+          <t>-8938</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-35417.44213935517</t>
+          <t>-34352.97788224091</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-31861.42593251113</t>
+          <t>-28498.42446811244</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.02</v>
+        <v>-1.34</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.22000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>58.08</v>
+        <v>58</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.1</v>
+        <v>60.13</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.77</v>
+        <v>-0.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.67</v>
+        <v>-0.68</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>812030.3550212164</t>
+          <t>813205.7563559322</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>188434.4</v>
+        <v>179557.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>211905.8</t>
+          <t>210593.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>549840.7</v>
+        <v>551119.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-23471</t>
+          <t>-31035</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-36063.99054059955</t>
+          <t>-35417.44213935517</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-37563.41281263391</t>
+          <t>-31861.42593251113</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>229092.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2961.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.69</v>
+        <v>-2.02</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>58.14</v>
+        <v>58.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.07</v>
+        <v>60.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-24.14</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.8</v>
+        <v>-0.77</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.65</v>
+        <v>-0.67</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.17</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>812030.3550212164</t>
+          <t>813205.7563559322</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>209836.2</v>
+        <v>188434.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>215755.9</t>
+          <t>211905.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>550120.9</v>
+        <v>549840.7</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5919</t>
+          <t>-23471</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-35791.36830932057</t>
+          <t>-36063.99054059955</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-38160.02218378661</t>
+          <t>-37563.41281263391</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>162030.0</t>
+          <t>171155.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>57.5</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>57.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ12"/>
+  <dimension ref="A1:CR12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,320 +551,360 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>MA_last_cross_d2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MA_last_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -883,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17140.0</t>
+          <t>29966.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>59.80</t>
+          <t>71.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,300 +1033,340 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>61.81</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>17140</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>95.77</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>29966</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>98.59</t>
         </is>
       </c>
-      <c r="AH2" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-2.43</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>59.72</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>58.98</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>410.51</t>
-        </is>
+      <c r="AP2" t="n">
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.19</v>
+        <v>6.29</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>62.23999999999999</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>59.77</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>59.11</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2399.21</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-103.59</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-99.28</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>813205.7563559322</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>1096143.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>840136.2</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>525749.3</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>433831.26</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>314386</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>30520.31719979418</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>159289.6279298227</t>
-        </is>
-      </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1096143.0</t>
+          <t>816177.9266572639</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
+          <t>1946983.0</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>1199492.4</v>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>697538.4</t>
+        </is>
+      </c>
+      <c r="BH2" t="n">
+        <v>456427.36</v>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>501953</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>61298.10510751283</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>230575.9385999654</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>1946983.0</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>7.81</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>2.76</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>47.2</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>37846</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>62.7</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
         <is>
           <t>64.7</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>64.8</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>63.1</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1305,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30630.0</t>
+          <t>17140.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>59.80</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,300 +1495,340 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>35.36</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-1.41</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>17140</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-2.67</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>59.4</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>58.08</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>59.68</v>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>29966</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>95.77</t>
+        </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.86</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>163.23</t>
-        </is>
+          <t>98.59</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.61</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-0.39</v>
+        <v>4.17</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-2.43</t>
+        </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>58.98</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>410.51</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-107.28</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-103.59</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>813205.7563559322</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>1939088.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>653003.2</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>433250.5</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>423371.84</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>219752</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>7107.715248879902</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>142924.5545464109</t>
-        </is>
-      </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1939088.0</t>
+          <t>816177.9266572639</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
+          <t>1096143.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>840136.2</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>525749.3</t>
+        </is>
+      </c>
+      <c r="BH3" t="n">
+        <v>433831.26</v>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>314386</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>30520.31719979418</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>159289.6279298227</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>1096143.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>8.32</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>7.81</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>47.2</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>37846</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>61.1</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>63.8</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>64.7</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>64.8</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>63.1</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>63.5</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1727,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10381.0</t>
+          <t>30630.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,300 +1957,340 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>63.18</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>17140</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>29966</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>75.76</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-2.93</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>57.98</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>57.91</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>59.65</v>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.74</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>57.05</t>
-        </is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>7.41</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-0.54</v>
+        <v>2.26</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-2.67</t>
+        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>58.08</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>58.86</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>163.23</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-110.25</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-107.28</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>813205.7563559322</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>627723.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>325263.2</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>255544.7</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>399545.28</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>69718</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-17586.25553248937</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>24125.89419345069</t>
-        </is>
-      </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>627723.0</t>
+          <t>816177.9266572639</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
+          <t>1939088.0</t>
+        </is>
+      </c>
+      <c r="BF4" t="n">
+        <v>653003.2</v>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>433250.5</t>
+        </is>
+      </c>
+      <c r="BH4" t="n">
+        <v>423371.84</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>219752</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>7107.715248879902</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>142924.5545464109</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>1939088.0</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>8.32</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>47.2</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>37846</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2139,7 +2299,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6619.0</t>
+          <t>10381.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,300 +2419,340 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>21.41</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>17140</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>29966</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>51.52</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-2.9</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>57.54</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>57.98</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>59.72</v>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.65</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>27.03</t>
-        </is>
+          <t>75.76</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.48</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-0.62</v>
+        <v>0.13</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-2.93</t>
+        </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>57.98</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>58.74</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>57.05</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-111.71</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-110.25</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>813205.7563559322</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>387525.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>231070.8</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>212700.8</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>426509.1</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>18370</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-25170.28275538756</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-5944.723960544128</t>
-        </is>
-      </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>387525.0</t>
+          <t>816177.9266572639</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
+          <t>627723.0</t>
+        </is>
+      </c>
+      <c r="BF5" t="n">
+        <v>325263.2</v>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>255544.7</t>
+        </is>
+      </c>
+      <c r="BH5" t="n">
+        <v>399545.28</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>69718</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>-17586.25553248937</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>24125.89419345069</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>627723.0</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>47.2</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>37846</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>57.3</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>59.2</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>57.2</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>59.2</t>
-        </is>
-      </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>60.1</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>61.4</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2571,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2635.0</t>
+          <t>6619.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,300 +2881,340 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>13.65</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>17140</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>27.27</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>28.6</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-2.96</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>57.14</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>58.02</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>59.79</v>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>29966</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.57</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
+          <t>51.52</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.88</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-0.66</v>
+        <v>-0.77</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-2.9</t>
+        </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>57.54</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>58.65</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>27.03</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-112.50</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-111.71</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>813205.7563559322</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>150202.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>195584.4</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>187571.1</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>459165.6</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>8013</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-28665.83889990455</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-22954.93832480302</t>
-        </is>
-      </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>150202.0</t>
+          <t>816177.9266572639</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
+          <t>387525.0</t>
+        </is>
+      </c>
+      <c r="BF6" t="n">
+        <v>231070.8</v>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>212700.8</t>
+        </is>
+      </c>
+      <c r="BH6" t="n">
+        <v>426509.1</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>18370</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>-25170.28275538756</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>-5944.723960544128</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>387525.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>47.2</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>37846</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2993,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2635.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3018,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3103,300 +3343,340 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>5.44</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>17140</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>29966</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
         <is>
           <t>27.27</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>40.02</t>
-        </is>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>-3.18</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-2.96</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>57.14</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>58.57</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-112.50</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>2025/12/02</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>816177.9266572639</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>150202.0</t>
+        </is>
+      </c>
+      <c r="BF7" t="n">
+        <v>195584.4</v>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>187571.1</t>
+        </is>
+      </c>
+      <c r="BH7" t="n">
+        <v>459165.6</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>8013</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>-28665.83889990455</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>-22954.93832480302</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>150202.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>47.2</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="AM7" t="n">
-        <v>58.02</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>59.93</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>58.52</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-112.58</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>813205.7563559322</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>160478.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>211362.4</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>199898.4</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>488500.72</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>11464</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-29704.18445901392</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-21007.96104785847</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>160478.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>47.2</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>37846</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>57.3</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>56.3</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
         <is>
           <t>57.0</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3415,410 +3695,450 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2826.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>-1.89</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>5264.0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/06/03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>29966</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>27.27</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>40.02</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-3.18</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>59.93</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>58.52</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-112.58</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>2025/12/02</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>816177.9266572639</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>160478.0</t>
+        </is>
+      </c>
+      <c r="BF8" t="n">
+        <v>211362.4</v>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>199898.4</t>
+        </is>
+      </c>
+      <c r="BH8" t="n">
+        <v>488500.72</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>11464</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>-29704.18445901392</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>-21007.96104785847</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>160478.0</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>2025/08/29</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-3.23</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>-1.228328584465341</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>47.44460114587924</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>32.54445648609581</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>17.51</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>14.09%</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>9.19%</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>47.2</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>光洋科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
         <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>10.71</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10.86</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>17140</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>43.75</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-3.31</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>58.02</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>60.01</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>58.45</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-112.62</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>813205.7563559322</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>300388.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>213497.8</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>211667.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>500099.3</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-31285.31598831491</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-18577.28061479991</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>300388.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/08/29</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-3.74</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>光洋科</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-1.228328584465341</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>47.44460114587924</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>32.54445648609581</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>17.51</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>14.09%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>9.19%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>47.2</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>37846</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>光洋科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>58.5</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>56.3</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3837,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2707.0</t>
+          <t>5264.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,300 +4267,340 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>10.86</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>17140</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>61.54</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>53.85</t>
-        </is>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>-3.52</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>57.97</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>60.08</v>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>29966</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>58.41</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>5.58</t>
-        </is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>-1.22</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="AR9" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-3.31</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>60.01</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>58.45</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
         <v>-0.67</v>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AZ9" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="BA9" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-112.64</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-112.62</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>813205.7563559322</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>156761.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>185826.2</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>199472.7</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>509521.28</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-13646</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-33595.86787440854</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-29431.76283133053</t>
-        </is>
-      </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>816177.9266572639</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
+          <t>300388.0</t>
+        </is>
+      </c>
+      <c r="BF9" t="n">
+        <v>213497.8</v>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>211667.0</t>
+        </is>
+      </c>
+      <c r="BH9" t="n">
+        <v>500099.3</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>-31285.31598831491</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>-18577.28061479991</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>300388.0</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-3.74</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>47.2</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>37846</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>56.7</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4249,7 +4609,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3642.0</t>
+          <t>2707.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,300 +4729,340 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>5.58</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>17140</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="AH10" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>-3.66</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.3</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>57.92</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>60.12</v>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>29966</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>61.54</t>
+        </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>58.33</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-2.26</t>
-        </is>
+          <t>53.85</t>
+        </is>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.52</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-0.68</v>
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>57.97</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>58.41</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>5.58</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-112.82</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-112.64</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>813205.7563559322</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>210093.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>194330.8</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>203269.7</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>548208.92</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-8938</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-34352.97788224091</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-28498.42446811244</t>
-        </is>
-      </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>816177.9266572639</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
+          <t>156761.0</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>185826.2</v>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>199472.7</t>
+        </is>
+      </c>
+      <c r="BH10" t="n">
+        <v>509521.28</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-13646</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>-33595.86787440854</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>-29431.76283133053</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>156761.0</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-2.89</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>47.2</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>37846</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
         <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>57.2</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4681,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,300 +5191,340 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>7.51</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-2.27</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>17140</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>61.54</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>49.08</t>
-        </is>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>-3.55</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>58</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>60.13</v>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>29966</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>38.46</t>
+        </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>58.25</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-4.05</t>
-        </is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.17</v>
       </c>
       <c r="AQ11" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>60.12</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>58.33</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>-2.26</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AZ11" t="n">
         <v>-0.68</v>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-112.75</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-112.82</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>813205.7563559322</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>229092.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>179557.8</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>210593.2</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>551119.74</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-31035</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-35417.44213935517</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-31861.42593251113</t>
-        </is>
-      </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>816177.9266572639</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
+          <t>210093.0</t>
+        </is>
+      </c>
+      <c r="BF11" t="n">
+        <v>194330.8</v>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>203269.7</t>
+        </is>
+      </c>
+      <c r="BH11" t="n">
+        <v>548208.92</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>-8938</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>-34352.97788224091</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>-28498.42446811244</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>210093.0</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-2.89</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>47.2</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>37846</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>57.6</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>57.3</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>58.7</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5108,7 +5548,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2961.0</t>
+          <t>3965.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,300 +5653,340 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>8.18</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>17140</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>34.13</t>
-        </is>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>-3.37</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>58.08</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>60.1</v>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>29966</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>61.54</t>
+        </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>58.16</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-14.26</t>
-        </is>
+          <t>49.08</t>
+        </is>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-0.67</v>
+        <v>-1.34</v>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-3.55</t>
+        </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>57.22000000000001</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>58</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>60.13</v>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>58.25</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>-4.05</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-112.62</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-112.75</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>813205.7563559322</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>171155.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>188434.4</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>211905.8</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>549840.7</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-23471</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-36063.99054059955</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-37563.41281263391</t>
-        </is>
-      </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>171155.0</t>
+          <t>816177.9266572639</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
+          <t>229092.0</t>
+        </is>
+      </c>
+      <c r="BF12" t="n">
+        <v>179557.8</v>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>210593.2</t>
+        </is>
+      </c>
+      <c r="BH12" t="n">
+        <v>551119.74</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>-31035</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>-35417.44213935517</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>-31861.42593251113</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>229092.0</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-2.38</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>47.2</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>37846</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>58.5</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29966.0</t>
+          <t>14350.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>71.96</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>61.81</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,66 +1094,66 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>98.59</t>
+          <t>96.51</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>3.95</v>
+        <v>1.52</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.29</v>
+        <v>7.44</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>62.23999999999999</t>
+          <t>63.23999999999999</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>58.55</v>
+        <v>58.86</v>
       </c>
       <c r="AV2" t="n">
-        <v>59.77</v>
+        <v>59.82</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>59.11</t>
+          <t>59.25</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2399.21</t>
+          <t>342.99</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>0.95</v>
+        <v>1.19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.04</v>
+        <v>0.27</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-99.28</t>
+          <t>-94.96</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>816177.9266572639</t>
+          <t>816977.6767605634</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>1946983.0</t>
+          <t>922667.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>1199492.4</v>
+        <v>1306520.8</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>697538.4</t>
+          <t>768795.8</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>456427.36</v>
+        <v>465869.9</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>501953</t>
+          <t>537725</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>61298.10510751283</t>
+          <t>82311.97472236722</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>230575.9385999654</t>
+          <t>197888.2576040663</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1946983.0</t>
+          <t>922667.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17140.0</t>
+          <t>29966.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>59.80</t>
+          <t>71.96</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>61.81</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,17 +1556,17 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>95.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1575,47 +1575,47 @@
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>4.61</v>
+        <v>3.95</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.17</v>
+        <v>6.29</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>62.23999999999999</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>58.27</v>
+        <v>58.55</v>
       </c>
       <c r="AV3" t="n">
-        <v>59.72</v>
+        <v>59.77</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>59.11</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>410.51</t>
+          <t>2399.21</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>0.59</v>
+        <v>0.95</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.19</v>
+        <v>0.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-103.59</t>
+          <t>-99.28</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>816177.9266572639</t>
+          <t>816977.6767605634</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>1096143.0</t>
+          <t>1946983.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>840136.2</v>
+        <v>1199492.4</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>525749.3</t>
+          <t>697538.4</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>433831.26</v>
+        <v>456427.36</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>314386</t>
+          <t>501953</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>30520.31719979418</t>
+          <t>61298.10510751283</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>159289.6279298227</t>
+          <t>230575.9385999654</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1096143.0</t>
+          <t>1946983.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1735,22 +1735,22 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>62.7</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
           <t>64.7</t>
-        </is>
-      </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>64.8</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>63.1</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>63.5</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30630.0</t>
+          <t>17140.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>59.80</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>35.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,66 +2018,66 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.77</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.59</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>7.41</v>
+        <v>4.61</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.26</v>
+        <v>4.17</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>58.08</v>
+        <v>58.27</v>
       </c>
       <c r="AV4" t="n">
-        <v>59.68</v>
+        <v>59.72</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>163.23</t>
+          <t>410.51</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>0.24</v>
+        <v>0.59</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.39</v>
+        <v>-0.19</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-107.28</t>
+          <t>-103.59</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>816177.9266572639</t>
+          <t>816977.6767605634</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>1939088.0</t>
+          <t>1096143.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>653003.2</v>
+        <v>840136.2</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>433250.5</t>
+          <t>525749.3</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>423371.84</v>
+        <v>433831.26</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>219752</t>
+          <t>314386</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>7107.715248879902</t>
+          <t>30520.31719979418</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>142924.5545464109</t>
+          <t>159289.6279298227</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1939088.0</t>
+          <t>1096143.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2197,22 +2197,22 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10381.0</t>
+          <t>30630.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,12 +2480,12 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2495,51 +2495,51 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>3.48</v>
+        <v>7.41</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.13</v>
+        <v>2.26</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>57.98</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>57.91</v>
+        <v>58.08</v>
       </c>
       <c r="AV5" t="n">
-        <v>59.65</v>
+        <v>59.68</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>58.74</t>
+          <t>58.86</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>163.23</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>-0.23</v>
+        <v>0.24</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.54</v>
+        <v>-0.39</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-110.25</t>
+          <t>-107.28</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>816177.9266572639</t>
+          <t>816977.6767605634</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>627723.0</t>
+          <t>1939088.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>325263.2</v>
+        <v>653003.2</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>255544.7</t>
+          <t>433250.5</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>399545.28</v>
+        <v>423371.84</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>219752</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-17586.25553248937</t>
+          <t>7107.715248879902</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>24125.89419345069</t>
+          <t>142924.5545464109</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>627723.0</t>
+          <t>1939088.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2659,22 +2659,22 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6619.0</t>
+          <t>10381.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>21.41</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,12 +2942,12 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2957,51 +2957,51 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>2.88</v>
+        <v>3.48</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.77</v>
+        <v>0.13</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.98</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>57.98</v>
+        <v>57.91</v>
       </c>
       <c r="AV6" t="n">
-        <v>59.72</v>
+        <v>59.65</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>58.74</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-0.45</v>
+        <v>-0.23</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.62</v>
+        <v>-0.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-111.71</t>
+          <t>-110.25</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>816177.9266572639</t>
+          <t>816977.6767605634</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>387525.0</t>
+          <t>627723.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>231070.8</v>
+        <v>325263.2</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>212700.8</t>
+          <t>255544.7</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>426509.1</v>
+        <v>399545.28</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>69718</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-25170.28275538756</t>
+          <t>-17586.25553248937</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-5944.723960544128</t>
+          <t>24125.89419345069</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>387525.0</t>
+          <t>627723.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3121,22 +3121,22 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2635.0</t>
+          <t>6619.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,66 +3404,66 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-0.25</v>
+        <v>2.88</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.53</v>
+        <v>-0.77</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>58.02</v>
+        <v>57.98</v>
       </c>
       <c r="AV7" t="n">
-        <v>59.79</v>
+        <v>59.72</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>58.57</t>
+          <t>58.65</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-0.65</v>
+        <v>-0.45</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.66</v>
+        <v>-0.62</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-112.50</t>
+          <t>-111.71</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>816177.9266572639</t>
+          <t>816977.6767605634</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>150202.0</t>
+          <t>387525.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>195584.4</v>
+        <v>231070.8</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>187571.1</t>
+          <t>212700.8</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>459165.6</v>
+        <v>426509.1</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-28665.83889990455</t>
+          <t>-25170.28275538756</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-22954.93832480302</t>
+          <t>-5944.723960544128</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>150202.0</t>
+          <t>387525.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3653,17 +3653,17 @@
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2635.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,12 +3866,12 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3881,52 +3881,52 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>-0.52</v>
+        <v>-0.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.25</v>
+        <v>-1.53</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AU8" t="n">
         <v>58.02</v>
       </c>
       <c r="AV8" t="n">
-        <v>59.93</v>
+        <v>59.79</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>58.52</t>
+          <t>58.57</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AY8" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>-0.66</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>-0.67</v>
-      </c>
       <c r="BA8" t="inlineStr">
         <is>
           <t>5.31</t>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-112.58</t>
+          <t>-112.50</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>816177.9266572639</t>
+          <t>816977.6767605634</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>160478.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>211362.4</v>
+        <v>195584.4</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>199898.4</t>
+          <t>187571.1</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>488500.72</v>
+        <v>459165.6</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-29704.18445901392</t>
+          <t>-28665.83889990455</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-21007.96104785847</t>
+          <t>-22954.93832480302</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>160478.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,17 +4110,17 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
@@ -4157,109 +4157,109 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2826.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>11.21</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>-1.89</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5264.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>-4.07</t>
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,63 +4328,63 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-1.22</v>
+        <v>-0.52</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.07</v>
+        <v>-1.25</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AU9" t="n">
         <v>58.02</v>
       </c>
       <c r="AV9" t="n">
-        <v>60.01</v>
+        <v>59.93</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>58.45</t>
+          <t>58.52</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AZ9" t="n">
         <v>-0.67</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.58</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>816177.9266572639</t>
+          <t>816977.6767605634</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>213497.8</v>
+        <v>211362.4</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>211667.0</t>
+          <t>199898.4</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>500099.3</v>
+        <v>488500.72</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-31285.31598831491</t>
+          <t>-29704.18445901392</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-18577.28061479991</t>
+          <t>-21007.96104785847</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2707.0</t>
+          <t>5264.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,63 +4790,63 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>0.52</v>
+        <v>-1.22</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.07</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>57.97</v>
+        <v>58.02</v>
       </c>
       <c r="AV10" t="n">
-        <v>60.08</v>
+        <v>60.01</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>58.45</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>-0.63</v>
+        <v>-0.67</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0.67</v>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-112.64</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>816177.9266572639</t>
+          <t>816977.6767605634</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>185826.2</v>
+        <v>213497.8</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>199472.7</t>
+          <t>211667.0</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>509521.28</v>
+        <v>500099.3</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-13646</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-33595.86787440854</t>
+          <t>-31285.31598831491</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-29431.76283133053</t>
+          <t>-18577.28061479991</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3642.0</t>
+          <t>2707.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-0.17</v>
+        <v>0.52</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.06</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>57.92</v>
+        <v>57.97</v>
       </c>
       <c r="AV11" t="n">
-        <v>60.12</v>
+        <v>60.08</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-0.7</v>
+        <v>-0.63</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-112.82</t>
+          <t>-112.64</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>816177.9266572639</t>
+          <t>816977.6767605634</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>194330.8</v>
+        <v>185826.2</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>203269.7</t>
+          <t>199472.7</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>548208.92</v>
+        <v>509521.28</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-8938</t>
+          <t>-13646</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-34352.97788224091</t>
+          <t>-33595.86787440854</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-28498.42446811244</t>
+          <t>-29431.76283133053</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3965.0</t>
+          <t>3642.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,59 +5714,59 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>-0.17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.34</v>
+        <v>-1.06</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>57.22000000000001</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>58</v>
+        <v>57.92</v>
       </c>
       <c r="AV12" t="n">
-        <v>60.13</v>
+        <v>60.12</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AY12" t="n">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.82</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>816177.9266572639</t>
+          <t>816977.6767605634</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>179557.8</v>
+        <v>194330.8</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>210593.2</t>
+          <t>203269.7</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>551119.74</v>
+        <v>548208.92</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-31035</t>
+          <t>-8938</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-35417.44213935517</t>
+          <t>-34352.97788224091</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-31861.42593251113</t>
+          <t>-28498.42446811244</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>229092.0</t>
+          <t>210093.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>29.60</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-1.38</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>14350</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>93.75</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>96.51</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>1.52</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>7.44</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-1.6</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>63.23999999999999</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>58.86</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>59.82</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>59.25</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>342.99</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>1.19</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>0.27</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-94.96</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>816977.6767605634</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>922667.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>1306520.8</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>768795.8</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>465869.9</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>537725</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>82311.97472236722</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>197888.2576040663</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>922667.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>9.00</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價跌量縮</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>2.79</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>27.32</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>38263</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>64.3</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>63.3</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>64.2</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>61.81</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>14350</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>98.59</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>3.95</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>6.29</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-2.04</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>62.23999999999999</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>58.55</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>59.77</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>59.11</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>2399.21</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>0.95</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>0.04</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-99.28</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>816977.6767605634</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>1946983.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>1199492.4</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>697538.4</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>456427.36</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>501953</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>61298.10510751283</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>230575.9385999654</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>1946983.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>9.85</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>2.82</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>27.32</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>38263</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>66.4</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>62.7</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>64.7</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>35.36</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-1.41</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>14350</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>95.77</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>98.59</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>4.61</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>4.17</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-2.43</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>58.27</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>59.72</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>58.98</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>410.51</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>0.59</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-0.19</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-103.59</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>816977.6767605634</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>1096143.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>840136.2</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>525749.3</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>433831.26</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>314386</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>30520.31719979418</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>159289.6279298227</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>1096143.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>7.81</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價跌量增</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>2.76</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>27.32</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>38263</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>64.7</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>64.8</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>63.1</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>63.5</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>63.18</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>4.17</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>14350</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>7.41</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>2.26</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-2.67</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>59.4</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>58.08</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>59.68</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>58.86</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>163.23</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>0.24</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-0.39</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-107.28</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>816977.6767605634</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>1939088.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>653003.2</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>433250.5</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>423371.84</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>219752</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>7107.715248879902</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>142924.5545464109</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>1939088.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>2.78</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>27.32</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>38263</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>61.1</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>64.4</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>63.8</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>21.41</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-1.66</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>14350</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>75.76</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>3.48</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>0.13</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-2.93</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>1.56</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>57.98</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>57.91</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>59.65</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>58.74</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>57.05</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.23</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-0.54</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-110.25</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>816977.6767605634</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>627723.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>325263.2</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>255544.7</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>399545.28</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>69718</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-17586.25553248937</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>24125.89419345069</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>627723.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>2.61</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>27.32</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>38263</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>60.1</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>61.4</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>59.6</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>60.0</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>13.65</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>14350</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>51.52</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>2.88</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>-0.77</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-2.9</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>57.54</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>57.98</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>59.72</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>58.65</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>27.03</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-0.45</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-0.62</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-111.71</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>816977.6767605634</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>387525.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>231070.8</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>212700.8</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>426509.1</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>18370</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-25170.28275538756</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-5944.723960544128</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>387525.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價漲量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>2.58</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>27.32</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>38263</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>59.2</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>57.2</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>59.2</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>5.44</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-0.52</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>14350</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>27.27</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>28.6</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-1.53</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-2.96</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>57.14</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>58.02</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>59.79</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>58.57</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>2.61</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-0.65</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-0.66</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-112.50</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>816977.6767605634</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>150202.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>195584.4</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>187571.1</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>459165.6</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>8013</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-28665.83889990455</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-22954.93832480302</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>150202.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-3.23</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>2.48</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>27.32</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>38263</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>57.7</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>56.6</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>57.0</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>5.83</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>14350</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>27.27</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>40.02</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>-0.52</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-1.25</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-3.18</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>2.41</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>58.02</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>59.93</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>58.52</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-0.66</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-0.67</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-112.58</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>816977.6767605634</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>160478.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>211362.4</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>199898.4</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>488500.72</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>11464</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-29704.18445901392</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-21007.96104785847</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>160478.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-3.23</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>2.48</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>27.32</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>38263</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>56.3</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>57.0</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>10.86</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-2.28</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>14350</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>43.75</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-1.22</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-1.07</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-3.31</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>2.66</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>57.4</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>58.02</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>60.01</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>58.45</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-0.67</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-0.67</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-112.62</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>816977.6767605634</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>300388.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>213497.8</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>211667.0</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>500099.3</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>1830</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-31285.31598831491</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-18577.28061479991</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>300388.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-3.74</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>2.47</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>27.32</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>38263</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>5.58</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-0.34</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>14350</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>61.54</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>53.85</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>0.52</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-3.52</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>2.87</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>57.5</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>57.97</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>60.08</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>58.41</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>5.58</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-0.63</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-0.67</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-112.64</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>816977.6767605634</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>156761.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>185826.2</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>199472.7</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>509521.28</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-13646</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-33595.86787440854</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-29431.76283133053</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>156761.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-1.87</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>2.52</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>27.32</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>38263</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>57.8</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>57.5</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>57.8</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>59.8</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/07/10</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>7.51</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-2.27</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>14350</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>38.46</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-1.06</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-3.66</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>3.07</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>57.92</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>60.12</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>58.33</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>-2.26</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-0.68</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>5.31</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-112.82</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>816977.6767605634</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>210093.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>194330.8</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>203269.7</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>548208.92</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-8938</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-34352.97788224091</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-28498.42446811244</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>210093.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>58.9</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/08/29</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-2.89</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>光洋科</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-1.228328584465341</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>47.44460114587924</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>32.54445648609581</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>2.49</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>17.51</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>27.32</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>9.19%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>38263</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>貴金屬材料79.52%、其他20.48% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>光洋科-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>58.7</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>57.0</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>57.2</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>22.98</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 半導體 - 化學品** 電腦及週邊設備 - 硬碟機** 平面顯示器 - 化學品(如光阻劑、靶材等)** 觸控面板 - ITO靶材** 被動元件 - 濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)** 印刷電路板 - 生產製程及檢測設備** 其他 - 環保潔能服務產業** 汽車 - 其他** 太陽能產業 - 材料</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14350.0</t>
+          <t>11741.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>69.94</t>
+          <t>60.62</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.60</t>
+          <t>24.22</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>55.84</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>96.51</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1.52</v>
+        <v>-3.46</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.44</v>
+        <v>7.53</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>63.23999999999999</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>58.86</v>
+        <v>59.05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>59.82</v>
+        <v>59.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>59.25</t>
+          <t>59.35</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>342.99</t>
+          <t>155.98</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-94.96</t>
+          <t>-91.74</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>816977.6767605634</t>
+          <t>817363.5084388186</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>922667.0</t>
+          <t>727536.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>1306520.8</v>
+        <v>1326483.4</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>768795.8</t>
+          <t>825873.3</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>465869.9</v>
+        <v>468962.64</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>537725</t>
+          <t>500610</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>82311.97472236722</t>
+          <t>93560.1092984392</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>197888.2576040663</t>
+          <t>155424.8494668351</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>922667.0</t>
+          <t>727536.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29966.0</t>
+          <t>14350.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>71.96</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>61.81</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>98.59</t>
+          <t>96.51</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>3.95</v>
+        <v>1.52</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.29</v>
+        <v>7.44</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>62.23999999999999</t>
+          <t>63.23999999999999</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>58.55</v>
+        <v>58.86</v>
       </c>
       <c r="AZ3" t="n">
-        <v>59.77</v>
+        <v>59.82</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>59.11</t>
+          <t>59.25</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2399.21</t>
+          <t>342.99</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.95</v>
+        <v>1.19</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.04</v>
+        <v>0.27</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-99.28</t>
+          <t>-94.96</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>816977.6767605634</t>
+          <t>817363.5084388186</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>1946983.0</t>
+          <t>922667.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>1199492.4</v>
+        <v>1306520.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>697538.4</t>
+          <t>768795.8</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>456427.36</v>
+        <v>465869.9</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>501953</t>
+          <t>537725</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>61298.10510751283</t>
+          <t>82311.97472236722</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>230575.9385999654</t>
+          <t>197888.2576040663</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>1946983.0</t>
+          <t>922667.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17140.0</t>
+          <t>29966.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>59.80</t>
+          <t>71.96</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>61.81</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,17 +2098,17 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>95.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2117,47 +2117,47 @@
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>4.61</v>
+        <v>3.95</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.17</v>
+        <v>6.29</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>62.23999999999999</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>58.27</v>
+        <v>58.55</v>
       </c>
       <c r="AZ4" t="n">
-        <v>59.72</v>
+        <v>59.77</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>59.11</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>410.51</t>
+          <t>2399.21</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.59</v>
+        <v>0.95</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.19</v>
+        <v>0.04</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-103.59</t>
+          <t>-99.28</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>816977.6767605634</t>
+          <t>817363.5084388186</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>1096143.0</t>
+          <t>1946983.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>840136.2</v>
+        <v>1199492.4</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>525749.3</t>
+          <t>697538.4</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>433831.26</v>
+        <v>456427.36</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>314386</t>
+          <t>501953</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>30520.31719979418</t>
+          <t>61298.10510751283</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>159289.6279298227</t>
+          <t>230575.9385999654</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>1096143.0</t>
+          <t>1946983.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>62.7</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
           <t>64.7</t>
-        </is>
-      </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>64.8</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>63.1</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>63.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30630.0</t>
+          <t>17140.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>59.80</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>35.36</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.77</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.59</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>7.41</v>
+        <v>4.61</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.26</v>
+        <v>4.17</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>58.08</v>
+        <v>58.27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>59.68</v>
+        <v>59.72</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>163.23</t>
+          <t>410.51</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.24</v>
+        <v>0.59</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.39</v>
+        <v>-0.19</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-107.28</t>
+          <t>-103.59</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>816977.6767605634</t>
+          <t>817363.5084388186</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>1939088.0</t>
+          <t>1096143.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>653003.2</v>
+        <v>840136.2</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>433250.5</t>
+          <t>525749.3</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>423371.84</v>
+        <v>433831.26</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>219752</t>
+          <t>314386</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>7107.715248879902</t>
+          <t>30520.31719979418</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>142924.5545464109</t>
+          <t>159289.6279298227</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1939088.0</t>
+          <t>1096143.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10381.0</t>
+          <t>30630.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,12 +3062,12 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3077,51 +3077,51 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>3.48</v>
+        <v>7.41</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.13</v>
+        <v>2.26</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>57.98</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>57.91</v>
+        <v>58.08</v>
       </c>
       <c r="AZ6" t="n">
-        <v>59.65</v>
+        <v>59.68</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>58.74</t>
+          <t>58.86</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>163.23</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.23</v>
+        <v>0.24</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.54</v>
+        <v>-0.39</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-110.25</t>
+          <t>-107.28</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>816977.6767605634</t>
+          <t>817363.5084388186</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>627723.0</t>
+          <t>1939088.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>325263.2</v>
+        <v>653003.2</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>255544.7</t>
+          <t>433250.5</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>399545.28</v>
+        <v>423371.84</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>219752</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-17586.25553248937</t>
+          <t>7107.715248879902</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>24125.89419345069</t>
+          <t>142924.5545464109</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>627723.0</t>
+          <t>1939088.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3343,7 +3343,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6619.0</t>
+          <t>10381.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>21.41</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3559,51 +3559,51 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>2.88</v>
+        <v>3.48</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.77</v>
+        <v>0.13</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.98</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>57.98</v>
+        <v>57.91</v>
       </c>
       <c r="AZ7" t="n">
-        <v>59.72</v>
+        <v>59.65</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>58.74</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.45</v>
+        <v>-0.23</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.62</v>
+        <v>-0.54</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-111.71</t>
+          <t>-110.25</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>816977.6767605634</t>
+          <t>817363.5084388186</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>387525.0</t>
+          <t>627723.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>231070.8</v>
+        <v>325263.2</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>212700.8</t>
+          <t>255544.7</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>426509.1</v>
+        <v>399545.28</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>69718</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-25170.28275538756</t>
+          <t>-17586.25553248937</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-5944.723960544128</t>
+          <t>24125.89419345069</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>387525.0</t>
+          <t>627723.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2635.0</t>
+          <t>6619.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.25</v>
+        <v>2.88</v>
       </c>
       <c r="AU8" t="n">
-        <v>-1.53</v>
+        <v>-0.77</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>58.02</v>
+        <v>57.98</v>
       </c>
       <c r="AZ8" t="n">
-        <v>59.79</v>
+        <v>59.72</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>58.57</t>
+          <t>58.65</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.65</v>
+        <v>-0.45</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.66</v>
+        <v>-0.62</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-112.50</t>
+          <t>-111.71</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>816977.6767605634</t>
+          <t>817363.5084388186</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>150202.0</t>
+          <t>387525.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>195584.4</v>
+        <v>231070.8</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>187571.1</t>
+          <t>212700.8</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>459165.6</v>
+        <v>426509.1</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-28665.83889990455</t>
+          <t>-25170.28275538756</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-22954.93832480302</t>
+          <t>-5944.723960544128</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>150202.0</t>
+          <t>387525.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2826.0</t>
+          <t>2635.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,12 +4508,12 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4523,52 +4523,52 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.52</v>
+        <v>-0.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>-1.25</v>
+        <v>-1.53</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AY9" t="n">
         <v>58.02</v>
       </c>
       <c r="AZ9" t="n">
-        <v>59.93</v>
+        <v>59.79</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>58.52</t>
+          <t>58.57</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BC9" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="BD9" t="n">
         <v>-0.66</v>
       </c>
-      <c r="BD9" t="n">
-        <v>-0.67</v>
-      </c>
       <c r="BE9" t="inlineStr">
         <is>
           <t>5.31</t>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-112.58</t>
+          <t>-112.50</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>816977.6767605634</t>
+          <t>817363.5084388186</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>160478.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>211362.4</v>
+        <v>195584.4</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>199898.4</t>
+          <t>187571.1</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>488500.72</v>
+        <v>459165.6</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-29704.18445901392</t>
+          <t>-28665.83889990455</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-21007.96104785847</t>
+          <t>-22954.93832480302</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>160478.0</t>
+          <t>150202.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,17 +4752,17 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
@@ -4799,187 +4799,187 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2826.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7.01</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>-1.89</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5264.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>11.68</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025/06/03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/07/10</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>58.1</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>61.5</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025/06/03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>59.8</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,63 +4990,63 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-1.22</v>
+        <v>-0.52</v>
       </c>
       <c r="AU10" t="n">
-        <v>-1.07</v>
+        <v>-1.25</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AY10" t="n">
         <v>58.02</v>
       </c>
       <c r="AZ10" t="n">
-        <v>60.01</v>
+        <v>59.93</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>58.45</t>
+          <t>58.52</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="BD10" t="n">
         <v>-0.67</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-112.62</t>
+          <t>-112.58</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>816977.6767605634</t>
+          <t>817363.5084388186</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>213497.8</v>
+        <v>211362.4</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>211667.0</t>
+          <t>199898.4</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>500099.3</v>
+        <v>488500.72</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-31285.31598831491</t>
+          <t>-29704.18445901392</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-18577.28061479991</t>
+          <t>-21007.96104785847</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>300388.0</t>
+          <t>160478.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2707.0</t>
+          <t>5264.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,63 +5472,63 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.52</v>
+        <v>-1.22</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.07</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>57.97</v>
+        <v>58.02</v>
       </c>
       <c r="AZ11" t="n">
-        <v>60.08</v>
+        <v>60.01</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>58.45</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.63</v>
+        <v>-0.67</v>
       </c>
       <c r="BD11" t="n">
         <v>-0.67</v>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-112.64</t>
+          <t>-112.62</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>816977.6767605634</t>
+          <t>817363.5084388186</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>185826.2</v>
+        <v>213497.8</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>199472.7</t>
+          <t>211667.0</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>509521.28</v>
+        <v>500099.3</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-13646</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-33595.86787440854</t>
+          <t>-31285.31598831491</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-29431.76283133053</t>
+          <t>-18577.28061479991</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>156761.0</t>
+          <t>300388.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3642.0</t>
+          <t>2707.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.17</v>
+        <v>0.52</v>
       </c>
       <c r="AU12" t="n">
-        <v>-1.06</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>57.92</v>
+        <v>57.97</v>
       </c>
       <c r="AZ12" t="n">
-        <v>60.12</v>
+        <v>60.08</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.7</v>
+        <v>-0.63</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-112.82</t>
+          <t>-112.64</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>816977.6767605634</t>
+          <t>817363.5084388186</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>194330.8</v>
+        <v>185826.2</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>203269.7</t>
+          <t>199472.7</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>548208.92</v>
+        <v>509521.28</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-8938</t>
+          <t>-13646</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-34352.97788224091</t>
+          <t>-33595.86787440854</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-28498.42446811244</t>
+          <t>-29431.76283133053</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>210093.0</t>
+          <t>156761.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
+        <is>
           <t>58.3</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
-      </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/ITO靶材.xlsx
+++ b/Result/checksun_type/ITO靶材.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11741.0</t>
+          <t>8740.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60.62</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>18.03</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>55.84</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-3.46</v>
+        <v>-0.16</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.53</v>
+        <v>6.84</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>59.05</v>
+        <v>59.34</v>
       </c>
       <c r="AZ2" t="n">
-        <v>59.8</v>
+        <v>59.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>59.35</t>
+          <t>59.48</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>155.98</t>
+          <t>105.11</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-91.74</t>
+          <t>-88.79</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>817363.5084388186</t>
+          <t>817369.7633426967</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>727536.0</t>
+          <t>547878.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>1326483.4</v>
+        <v>1048241.4</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>825873.3</t>
+          <t>850622.3</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>468962.64</v>
+        <v>473246.04</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>500610</t>
+          <t>197619</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>93560.1092984392</t>
+          <t>95834.01441161818</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>155424.8494668351</t>
+          <t>108340.4925341025</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>727536.0</t>
+          <t>547878.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>26.94</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>36535</t>
+          <t>37727</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14350.0</t>
+          <t>11741.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>69.94</t>
+          <t>60.62</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.60</t>
+          <t>24.22</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>55.84</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>96.51</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1.52</v>
+        <v>-3.46</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.44</v>
+        <v>7.53</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>63.23999999999999</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>58.86</v>
+        <v>59.05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>59.82</v>
+        <v>59.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>59.25</t>
+          <t>59.35</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>342.99</t>
+          <t>155.98</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-94.96</t>
+          <t>-91.74</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>817363.5084388186</t>
+          <t>817369.7633426967</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>922667.0</t>
+          <t>727536.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>1306520.8</v>
+        <v>1326483.4</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>768795.8</t>
+          <t>825873.3</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>465869.9</v>
+        <v>468962.64</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>537725</t>
+          <t>500610</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>82311.97472236722</t>
+          <t>93560.1092984392</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>197888.2576040663</t>
+          <t>155424.8494668351</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>922667.0</t>
+          <t>727536.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>26.94</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>36535</t>
+          <t>37727</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29966.0</t>
+          <t>14350.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>71.96</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>61.81</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>98.59</t>
+          <t>96.51</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>3.95</v>
+        <v>1.52</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.29</v>
+        <v>7.44</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>62.23999999999999</t>
+          <t>63.23999999999999</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>58.55</v>
+        <v>58.86</v>
       </c>
       <c r="AZ4" t="n">
-        <v>59.77</v>
+        <v>59.82</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>59.11</t>
+          <t>59.25</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>2399.21</t>
+          <t>342.99</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.95</v>
+        <v>1.19</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.04</v>
+        <v>0.27</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-99.28</t>
+          <t>-94.96</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>817363.5084388186</t>
+          <t>817369.7633426967</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>1946983.0</t>
+          <t>922667.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>1199492.4</v>
+        <v>1306520.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>697538.4</t>
+          <t>768795.8</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>456427.36</v>
+        <v>465869.9</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>501953</t>
+          <t>537725</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>61298.10510751283</t>
+          <t>82311.97472236722</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>230575.9385999654</t>
+          <t>197888.2576040663</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>1946983.0</t>
+          <t>922667.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>26.94</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>36535</t>
+          <t>37727</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17140.0</t>
+          <t>29966.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>59.80</t>
+          <t>71.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>61.81</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,17 +2580,17 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>95.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2599,47 +2599,47 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>4.61</v>
+        <v>3.95</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.17</v>
+        <v>6.29</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>62.23999999999999</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>58.27</v>
+        <v>58.55</v>
       </c>
       <c r="AZ5" t="n">
-        <v>59.72</v>
+        <v>59.77</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>59.11</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>410.51</t>
+          <t>2399.21</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.59</v>
+        <v>0.95</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.19</v>
+        <v>0.04</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-103.59</t>
+          <t>-99.28</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>817363.5084388186</t>
+          <t>817369.7633426967</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>1096143.0</t>
+          <t>1946983.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>840136.2</v>
+        <v>1199492.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>525749.3</t>
+          <t>697538.4</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>433831.26</v>
+        <v>456427.36</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>314386</t>
+          <t>501953</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>30520.31719979418</t>
+          <t>61298.10510751283</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>159289.6279298227</t>
+          <t>230575.9385999654</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1096143.0</t>
+          <t>1946983.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>26.94</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>36535</t>
+          <t>37727</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,24 +2824,24 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>62.7</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
           <t>64.7</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
-        <is>
-          <t>64.8</t>
-        </is>
-      </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>63.1</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
-      </c>
       <c r="CT5" t="inlineStr">
         <is>
           <t>22.98</t>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30630.0</t>
+          <t>17140.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>59.80</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>35.36</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.77</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.59</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>7.41</v>
+        <v>4.61</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.26</v>
+        <v>4.17</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>58.08</v>
+        <v>58.27</v>
       </c>
       <c r="AZ6" t="n">
-        <v>59.68</v>
+        <v>59.72</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>163.23</t>
+          <t>410.51</t>
         </is>
       </c>
       <c r="BC